--- a/etl/3_carga/pruebacarga.xlsx
+++ b/etl/3_carga/pruebacarga.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quantum-Malloco\Desktop\Ventilacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quantum-Malloco\mediociones-confort-termico\etl\3_carga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CA9D3C4-591C-4DAD-8447-DD8E46EB58D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FD66F0-376F-4788-80FC-3E8BF597EE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="4440" windowWidth="20730" windowHeight="11160" xr2:uid="{7886A274-FF15-4EC9-B530-506EFDDC984E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7886A274-FF15-4EC9-B530-506EFDDC984E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="1175">
   <si>
     <t>Cerrado</t>
   </si>
@@ -126,36 +126,15 @@
     <t>Jefe de Sala</t>
   </si>
   <si>
-    <t>Francesca Aravena Santibañez</t>
-  </si>
-  <si>
     <t>Cristian Marquez</t>
   </si>
   <si>
     <t>2025-10-02T00:00:00</t>
   </si>
   <si>
-    <t>Av. Julio Buschmann #2223, Osorno</t>
-  </si>
-  <si>
     <t>10:30:00</t>
   </si>
   <si>
-    <t>Unimarc orienre</t>
-  </si>
-  <si>
-    <t>81537600-5</t>
-  </si>
-  <si>
-    <t>RENDIC HERMANOS S.A</t>
-  </si>
-  <si>
-    <t>Hoja_terreno</t>
-  </si>
-  <si>
-    <t>C:\Users\Quantum-Malloco\Desktop\Ventilacion\Casos de prueba 3\Normalizados\procesadas\Hoja de Terreno Ventilación y Provisión de Aire IST -unimarc oriente_normalizado_procesado.xlsx</t>
-  </si>
-  <si>
     <t>Pendiente</t>
   </si>
   <si>
@@ -216,33 +195,15 @@
     <t>Administrador</t>
   </si>
   <si>
-    <t>Anais Espinoza Salas</t>
-  </si>
-  <si>
     <t>Luis Núñez</t>
   </si>
   <si>
     <t>2025-09-02T00:00:00</t>
   </si>
   <si>
-    <t>Av. 21 de mayo #819</t>
-  </si>
-  <si>
     <t>10:00:00</t>
   </si>
   <si>
-    <t>S10 21 de Mayo</t>
-  </si>
-  <si>
-    <t>76.012.833-3</t>
-  </si>
-  <si>
-    <t>Super 10 S.A.</t>
-  </si>
-  <si>
-    <t>C:\Users\Quantum-Malloco\Desktop\Ventilacion\Casos de prueba 3\Normalizados\procesadas\Hoja de Terreno Ventilación y Provisión de Aire IST - s10 21 de mayo_normalizado_procesado.xlsx</t>
-  </si>
-  <si>
     <t>Estado</t>
   </si>
   <si>
@@ -3591,41 +3552,34 @@
     <t>FECHA DE VISITA</t>
   </si>
   <si>
-    <t>DIRECCIÓN (CT)</t>
-  </si>
-  <si>
     <t>HORARIO DE MEDICIÓN</t>
   </si>
   <si>
-    <t>NOMBRE DEL CENTRO DE TRABAJO (CT)</t>
-  </si>
-  <si>
-    <t>RUT EMPRESA</t>
-  </si>
-  <si>
-    <t>RAZON SOCIAL EMPRESA</t>
-  </si>
-  <si>
-    <t>__hits__</t>
-  </si>
-  <si>
-    <t>__sheet__</t>
-  </si>
-  <si>
-    <t>__source_file__</t>
-  </si>
-  <si>
-    <t>CUV</t>
+    <t>cuv_visita</t>
+  </si>
+  <si>
+    <t>anais.espinoza@ist.cl</t>
+  </si>
+  <si>
+    <t>francesca.aravena@ist.cl</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3660,15 +3614,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3981,4032 +3938,3977 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEB3C44-CD1B-4A23-B671-8545283FAE17}">
-  <dimension ref="A1:AQG3"/>
+  <dimension ref="A1:APZ3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1125" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1118" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1192</v>
+        <v>1172</v>
       </c>
       <c r="B1" t="s">
-        <v>1191</v>
+        <v>1171</v>
       </c>
       <c r="C1" t="s">
-        <v>1190</v>
+        <v>1170</v>
       </c>
       <c r="D1" t="s">
-        <v>1189</v>
+        <v>1169</v>
       </c>
       <c r="E1" t="s">
-        <v>1188</v>
+        <v>1168</v>
       </c>
       <c r="F1" t="s">
-        <v>1187</v>
+        <v>1167</v>
       </c>
       <c r="G1" t="s">
-        <v>1186</v>
+        <v>1166</v>
       </c>
       <c r="H1" t="s">
-        <v>1185</v>
+        <v>1165</v>
       </c>
       <c r="I1" t="s">
-        <v>1184</v>
+        <v>1164</v>
       </c>
       <c r="J1" t="s">
-        <v>1183</v>
+        <v>1163</v>
       </c>
       <c r="K1" t="s">
-        <v>1182</v>
+        <v>1162</v>
       </c>
       <c r="L1" t="s">
-        <v>1181</v>
+        <v>1161</v>
       </c>
       <c r="M1" t="s">
-        <v>1180</v>
+        <v>1160</v>
       </c>
       <c r="N1" t="s">
-        <v>1179</v>
+        <v>1159</v>
       </c>
       <c r="O1" t="s">
-        <v>1178</v>
+        <v>1158</v>
       </c>
       <c r="P1" t="s">
-        <v>1177</v>
+        <v>1157</v>
       </c>
       <c r="Q1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="R1" t="s">
-        <v>1175</v>
+        <v>1156</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>1155</v>
       </c>
       <c r="S1" t="s">
-        <v>1174</v>
+        <v>1154</v>
       </c>
       <c r="T1" t="s">
-        <v>1173</v>
+        <v>1153</v>
       </c>
       <c r="U1" t="s">
-        <v>1172</v>
+        <v>1152</v>
       </c>
       <c r="V1" t="s">
-        <v>1171</v>
-      </c>
-      <c r="W1" t="s">
-        <v>1170</v>
+        <v>1151</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>1150</v>
       </c>
       <c r="X1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>1168</v>
+        <v>1149</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1148</v>
       </c>
       <c r="Z1" t="s">
-        <v>1167</v>
+        <v>1147</v>
       </c>
       <c r="AA1" t="s">
-        <v>1166</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>1165</v>
+        <v>1146</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>1145</v>
       </c>
       <c r="AC1" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>1163</v>
+        <v>1144</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1143</v>
       </c>
       <c r="AE1" t="s">
-        <v>1162</v>
+        <v>1142</v>
       </c>
       <c r="AF1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>1160</v>
+        <v>1141</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>1140</v>
       </c>
       <c r="AH1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>1158</v>
+        <v>1139</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>1138</v>
       </c>
       <c r="AJ1" t="s">
-        <v>1157</v>
+        <v>1137</v>
       </c>
       <c r="AK1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>1155</v>
+        <v>1136</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>1135</v>
       </c>
       <c r="AM1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="AN1" s="2" t="s">
-        <v>1153</v>
+        <v>1134</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>1133</v>
       </c>
       <c r="AO1" t="s">
-        <v>1152</v>
+        <v>1132</v>
       </c>
       <c r="AP1" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>1150</v>
+        <v>1131</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>1130</v>
       </c>
       <c r="AR1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AS1" s="2" t="s">
-        <v>1148</v>
+        <v>1129</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>1128</v>
       </c>
       <c r="AT1" t="s">
-        <v>1147</v>
+        <v>1127</v>
       </c>
       <c r="AU1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>1145</v>
+        <v>1126</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>1125</v>
       </c>
       <c r="AW1" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AX1" s="2" t="s">
-        <v>1143</v>
+        <v>1124</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>1123</v>
       </c>
       <c r="AY1" t="s">
-        <v>1142</v>
+        <v>1122</v>
       </c>
       <c r="AZ1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>1140</v>
+        <v>1121</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>1120</v>
       </c>
       <c r="BB1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="BC1" s="2" t="s">
-        <v>1138</v>
+        <v>1119</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>1118</v>
       </c>
       <c r="BD1" t="s">
-        <v>1137</v>
+        <v>1117</v>
       </c>
       <c r="BE1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>1135</v>
+        <v>1116</v>
+      </c>
+      <c r="BF1" s="2" t="s">
+        <v>1115</v>
       </c>
       <c r="BG1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="BH1" s="2" t="s">
-        <v>1133</v>
+        <v>1114</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>1113</v>
       </c>
       <c r="BI1" t="s">
-        <v>1132</v>
+        <v>1112</v>
       </c>
       <c r="BJ1" t="s">
-        <v>1131</v>
+        <v>1111</v>
       </c>
       <c r="BK1" t="s">
-        <v>1130</v>
+        <v>1110</v>
       </c>
       <c r="BL1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="BM1" s="2" t="s">
-        <v>1128</v>
+        <v>1109</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>1108</v>
       </c>
       <c r="BN1" t="s">
-        <v>1127</v>
+        <v>1107</v>
       </c>
       <c r="BO1" t="s">
-        <v>1126</v>
+        <v>1106</v>
       </c>
       <c r="BP1" t="s">
-        <v>1125</v>
+        <v>1105</v>
       </c>
       <c r="BQ1" t="s">
-        <v>1124</v>
+        <v>1104</v>
       </c>
       <c r="BR1" t="s">
-        <v>1123</v>
+        <v>1103</v>
       </c>
       <c r="BS1" t="s">
-        <v>1122</v>
+        <v>1102</v>
       </c>
       <c r="BT1" t="s">
-        <v>1121</v>
+        <v>1101</v>
       </c>
       <c r="BU1" t="s">
-        <v>1120</v>
+        <v>1100</v>
       </c>
       <c r="BV1" t="s">
-        <v>1119</v>
+        <v>1099</v>
       </c>
       <c r="BW1" t="s">
-        <v>1118</v>
+        <v>1098</v>
       </c>
       <c r="BX1" t="s">
-        <v>1117</v>
+        <v>1097</v>
       </c>
       <c r="BY1" t="s">
-        <v>1116</v>
+        <v>1096</v>
       </c>
       <c r="BZ1" t="s">
-        <v>1115</v>
+        <v>1095</v>
       </c>
       <c r="CA1" t="s">
-        <v>1114</v>
+        <v>1094</v>
       </c>
       <c r="CB1" t="s">
-        <v>1113</v>
+        <v>1093</v>
       </c>
       <c r="CC1" t="s">
-        <v>1112</v>
+        <v>1092</v>
       </c>
       <c r="CD1" t="s">
-        <v>1111</v>
+        <v>1091</v>
       </c>
       <c r="CE1" t="s">
-        <v>1110</v>
+        <v>1090</v>
       </c>
       <c r="CF1" t="s">
-        <v>1109</v>
+        <v>1089</v>
       </c>
       <c r="CG1" t="s">
-        <v>1108</v>
+        <v>1088</v>
       </c>
       <c r="CH1" t="s">
-        <v>1107</v>
+        <v>1087</v>
       </c>
       <c r="CI1" t="s">
-        <v>1106</v>
+        <v>1086</v>
       </c>
       <c r="CJ1" t="s">
-        <v>1105</v>
+        <v>1085</v>
       </c>
       <c r="CK1" t="s">
-        <v>1104</v>
+        <v>1084</v>
       </c>
       <c r="CL1" t="s">
-        <v>1103</v>
+        <v>1083</v>
       </c>
       <c r="CM1" t="s">
-        <v>1102</v>
+        <v>1082</v>
       </c>
       <c r="CN1" t="s">
-        <v>1101</v>
+        <v>1081</v>
       </c>
       <c r="CO1" t="s">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="CP1" t="s">
-        <v>1099</v>
+        <v>1079</v>
       </c>
       <c r="CQ1" t="s">
-        <v>1098</v>
+        <v>1078</v>
       </c>
       <c r="CR1" t="s">
-        <v>1097</v>
+        <v>1077</v>
       </c>
       <c r="CS1" t="s">
-        <v>1096</v>
+        <v>1076</v>
       </c>
       <c r="CT1" t="s">
-        <v>1095</v>
+        <v>1075</v>
       </c>
       <c r="CU1" t="s">
-        <v>1094</v>
+        <v>1074</v>
       </c>
       <c r="CV1" t="s">
-        <v>1093</v>
+        <v>1073</v>
       </c>
       <c r="CW1" t="s">
-        <v>1092</v>
+        <v>1072</v>
       </c>
       <c r="CX1" t="s">
-        <v>1091</v>
+        <v>1071</v>
       </c>
       <c r="CY1" t="s">
-        <v>1090</v>
+        <v>1070</v>
       </c>
       <c r="CZ1" t="s">
-        <v>1089</v>
+        <v>1069</v>
       </c>
       <c r="DA1" t="s">
-        <v>1088</v>
+        <v>1068</v>
       </c>
       <c r="DB1" t="s">
-        <v>1087</v>
+        <v>1067</v>
       </c>
       <c r="DC1" t="s">
-        <v>1086</v>
+        <v>1066</v>
       </c>
       <c r="DD1" t="s">
-        <v>1085</v>
+        <v>1065</v>
       </c>
       <c r="DE1" t="s">
-        <v>1084</v>
+        <v>1064</v>
       </c>
       <c r="DF1" t="s">
-        <v>1083</v>
+        <v>1063</v>
       </c>
       <c r="DG1" t="s">
-        <v>1082</v>
+        <v>1062</v>
       </c>
       <c r="DH1" t="s">
-        <v>1081</v>
+        <v>1061</v>
       </c>
       <c r="DI1" t="s">
-        <v>1080</v>
+        <v>1060</v>
       </c>
       <c r="DJ1" t="s">
-        <v>1079</v>
+        <v>1059</v>
       </c>
       <c r="DK1" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="DL1" t="s">
-        <v>1077</v>
+        <v>1057</v>
       </c>
       <c r="DM1" t="s">
-        <v>1076</v>
+        <v>1056</v>
       </c>
       <c r="DN1" t="s">
-        <v>1075</v>
+        <v>1055</v>
       </c>
       <c r="DO1" t="s">
-        <v>1074</v>
+        <v>1054</v>
       </c>
       <c r="DP1" t="s">
-        <v>1073</v>
+        <v>1053</v>
       </c>
       <c r="DQ1" t="s">
-        <v>1072</v>
+        <v>1052</v>
       </c>
       <c r="DR1" t="s">
-        <v>1071</v>
+        <v>1051</v>
       </c>
       <c r="DS1" t="s">
-        <v>1070</v>
+        <v>1050</v>
       </c>
       <c r="DT1" t="s">
-        <v>1069</v>
+        <v>1049</v>
       </c>
       <c r="DU1" t="s">
-        <v>1068</v>
+        <v>1048</v>
       </c>
       <c r="DV1" t="s">
-        <v>1067</v>
+        <v>1047</v>
       </c>
       <c r="DW1" t="s">
-        <v>1066</v>
+        <v>1046</v>
       </c>
       <c r="DX1" t="s">
-        <v>1065</v>
+        <v>1045</v>
       </c>
       <c r="DY1" t="s">
-        <v>1064</v>
+        <v>1044</v>
       </c>
       <c r="DZ1" t="s">
-        <v>1063</v>
+        <v>1043</v>
       </c>
       <c r="EA1" t="s">
-        <v>1062</v>
+        <v>1042</v>
       </c>
       <c r="EB1" t="s">
-        <v>1061</v>
+        <v>1041</v>
       </c>
       <c r="EC1" t="s">
-        <v>1060</v>
+        <v>1040</v>
       </c>
       <c r="ED1" t="s">
-        <v>1059</v>
+        <v>1039</v>
       </c>
       <c r="EE1" t="s">
-        <v>1058</v>
+        <v>1038</v>
       </c>
       <c r="EF1" t="s">
-        <v>1057</v>
+        <v>1037</v>
       </c>
       <c r="EG1" t="s">
-        <v>1056</v>
+        <v>1036</v>
       </c>
       <c r="EH1" t="s">
-        <v>1055</v>
+        <v>1035</v>
       </c>
       <c r="EI1" t="s">
-        <v>1054</v>
+        <v>1034</v>
       </c>
       <c r="EJ1" t="s">
-        <v>1053</v>
+        <v>1033</v>
       </c>
       <c r="EK1" t="s">
-        <v>1052</v>
+        <v>1032</v>
       </c>
       <c r="EL1" t="s">
-        <v>1051</v>
+        <v>1031</v>
       </c>
       <c r="EM1" t="s">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="EN1" t="s">
-        <v>1049</v>
+        <v>1029</v>
       </c>
       <c r="EO1" t="s">
-        <v>1048</v>
+        <v>1028</v>
       </c>
       <c r="EP1" t="s">
-        <v>1047</v>
+        <v>1027</v>
       </c>
       <c r="EQ1" t="s">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="ER1" t="s">
-        <v>1045</v>
+        <v>1025</v>
       </c>
       <c r="ES1" t="s">
-        <v>1044</v>
+        <v>1024</v>
       </c>
       <c r="ET1" t="s">
-        <v>1043</v>
+        <v>1023</v>
       </c>
       <c r="EU1" t="s">
-        <v>1042</v>
+        <v>1022</v>
       </c>
       <c r="EV1" t="s">
-        <v>1041</v>
+        <v>1021</v>
       </c>
       <c r="EW1" t="s">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="EX1" t="s">
-        <v>1039</v>
+        <v>1019</v>
       </c>
       <c r="EY1" t="s">
-        <v>1038</v>
+        <v>1018</v>
       </c>
       <c r="EZ1" t="s">
-        <v>1037</v>
+        <v>1017</v>
       </c>
       <c r="FA1" t="s">
-        <v>1036</v>
+        <v>1016</v>
       </c>
       <c r="FB1" t="s">
-        <v>1035</v>
+        <v>1015</v>
       </c>
       <c r="FC1" t="s">
-        <v>1034</v>
+        <v>1014</v>
       </c>
       <c r="FD1" t="s">
-        <v>1033</v>
+        <v>1013</v>
       </c>
       <c r="FE1" t="s">
-        <v>1032</v>
+        <v>1012</v>
       </c>
       <c r="FF1" t="s">
-        <v>1031</v>
+        <v>1011</v>
       </c>
       <c r="FG1" t="s">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="FH1" t="s">
-        <v>1029</v>
+        <v>1009</v>
       </c>
       <c r="FI1" t="s">
-        <v>1028</v>
+        <v>1008</v>
       </c>
       <c r="FJ1" t="s">
-        <v>1027</v>
+        <v>1007</v>
       </c>
       <c r="FK1" t="s">
-        <v>1026</v>
+        <v>1006</v>
       </c>
       <c r="FL1" t="s">
-        <v>1025</v>
+        <v>1005</v>
       </c>
       <c r="FM1" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="FN1" t="s">
-        <v>1023</v>
+        <v>1003</v>
       </c>
       <c r="FO1" t="s">
-        <v>1022</v>
+        <v>1002</v>
       </c>
       <c r="FP1" t="s">
-        <v>1021</v>
+        <v>1001</v>
       </c>
       <c r="FQ1" t="s">
-        <v>1020</v>
+        <v>1000</v>
       </c>
       <c r="FR1" t="s">
-        <v>1019</v>
+        <v>999</v>
       </c>
       <c r="FS1" t="s">
-        <v>1018</v>
+        <v>998</v>
       </c>
       <c r="FT1" t="s">
-        <v>1017</v>
+        <v>997</v>
       </c>
       <c r="FU1" t="s">
-        <v>1016</v>
+        <v>996</v>
       </c>
       <c r="FV1" t="s">
-        <v>1015</v>
+        <v>995</v>
       </c>
       <c r="FW1" t="s">
-        <v>1014</v>
+        <v>994</v>
       </c>
       <c r="FX1" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="FY1" t="s">
-        <v>1012</v>
+        <v>992</v>
       </c>
       <c r="FZ1" t="s">
-        <v>1011</v>
+        <v>991</v>
       </c>
       <c r="GA1" t="s">
-        <v>1010</v>
+        <v>990</v>
       </c>
       <c r="GB1" t="s">
-        <v>1009</v>
+        <v>989</v>
       </c>
       <c r="GC1" t="s">
-        <v>1008</v>
+        <v>988</v>
       </c>
       <c r="GD1" t="s">
-        <v>1007</v>
+        <v>987</v>
       </c>
       <c r="GE1" t="s">
-        <v>1006</v>
+        <v>986</v>
       </c>
       <c r="GF1" t="s">
-        <v>1005</v>
+        <v>985</v>
       </c>
       <c r="GG1" t="s">
-        <v>1004</v>
+        <v>984</v>
       </c>
       <c r="GH1" t="s">
-        <v>1003</v>
+        <v>983</v>
       </c>
       <c r="GI1" t="s">
-        <v>1002</v>
+        <v>982</v>
       </c>
       <c r="GJ1" t="s">
-        <v>1001</v>
+        <v>981</v>
       </c>
       <c r="GK1" t="s">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="GL1" t="s">
-        <v>999</v>
+        <v>979</v>
       </c>
       <c r="GM1" t="s">
-        <v>998</v>
+        <v>978</v>
       </c>
       <c r="GN1" t="s">
-        <v>997</v>
+        <v>977</v>
       </c>
       <c r="GO1" t="s">
-        <v>996</v>
+        <v>976</v>
       </c>
       <c r="GP1" t="s">
-        <v>995</v>
+        <v>975</v>
       </c>
       <c r="GQ1" t="s">
-        <v>994</v>
+        <v>974</v>
       </c>
       <c r="GR1" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="GS1" t="s">
-        <v>992</v>
+        <v>972</v>
       </c>
       <c r="GT1" t="s">
-        <v>991</v>
+        <v>971</v>
       </c>
       <c r="GU1" t="s">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="GV1" t="s">
-        <v>989</v>
+        <v>969</v>
       </c>
       <c r="GW1" t="s">
-        <v>988</v>
+        <v>968</v>
       </c>
       <c r="GX1" t="s">
-        <v>987</v>
+        <v>967</v>
       </c>
       <c r="GY1" t="s">
-        <v>986</v>
+        <v>966</v>
       </c>
       <c r="GZ1" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="HA1" t="s">
-        <v>984</v>
+        <v>964</v>
       </c>
       <c r="HB1" t="s">
-        <v>983</v>
+        <v>963</v>
       </c>
       <c r="HC1" t="s">
-        <v>982</v>
+        <v>962</v>
       </c>
       <c r="HD1" t="s">
-        <v>981</v>
+        <v>961</v>
       </c>
       <c r="HE1" t="s">
-        <v>980</v>
+        <v>960</v>
       </c>
       <c r="HF1" t="s">
-        <v>979</v>
+        <v>959</v>
       </c>
       <c r="HG1" t="s">
-        <v>978</v>
+        <v>958</v>
       </c>
       <c r="HH1" t="s">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="HI1" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="HJ1" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
       <c r="HK1" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
       <c r="HL1" t="s">
-        <v>973</v>
+        <v>953</v>
       </c>
       <c r="HM1" t="s">
-        <v>972</v>
+        <v>952</v>
       </c>
       <c r="HN1" t="s">
-        <v>971</v>
+        <v>951</v>
       </c>
       <c r="HO1" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="HP1" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="HQ1" t="s">
-        <v>968</v>
+        <v>948</v>
       </c>
       <c r="HR1" t="s">
-        <v>967</v>
+        <v>947</v>
       </c>
       <c r="HS1" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
       <c r="HT1" t="s">
-        <v>965</v>
+        <v>945</v>
       </c>
       <c r="HU1" t="s">
-        <v>964</v>
+        <v>944</v>
       </c>
       <c r="HV1" t="s">
-        <v>963</v>
+        <v>943</v>
       </c>
       <c r="HW1" t="s">
-        <v>962</v>
+        <v>942</v>
       </c>
       <c r="HX1" t="s">
-        <v>961</v>
+        <v>941</v>
       </c>
       <c r="HY1" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="HZ1" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="IA1" t="s">
-        <v>958</v>
+        <v>938</v>
       </c>
       <c r="IB1" t="s">
-        <v>957</v>
+        <v>937</v>
       </c>
       <c r="IC1" t="s">
-        <v>956</v>
+        <v>936</v>
       </c>
       <c r="ID1" t="s">
-        <v>955</v>
+        <v>935</v>
       </c>
       <c r="IE1" t="s">
-        <v>954</v>
+        <v>934</v>
       </c>
       <c r="IF1" t="s">
-        <v>953</v>
+        <v>933</v>
       </c>
       <c r="IG1" t="s">
-        <v>952</v>
+        <v>932</v>
       </c>
       <c r="IH1" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="II1" t="s">
-        <v>950</v>
+        <v>930</v>
       </c>
       <c r="IJ1" t="s">
-        <v>949</v>
+        <v>929</v>
       </c>
       <c r="IK1" t="s">
-        <v>948</v>
+        <v>928</v>
       </c>
       <c r="IL1" t="s">
-        <v>947</v>
+        <v>927</v>
       </c>
       <c r="IM1" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="IN1" t="s">
-        <v>945</v>
+        <v>925</v>
       </c>
       <c r="IO1" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="IP1" t="s">
-        <v>943</v>
+        <v>923</v>
       </c>
       <c r="IQ1" t="s">
-        <v>942</v>
+        <v>922</v>
       </c>
       <c r="IR1" t="s">
-        <v>941</v>
+        <v>921</v>
       </c>
       <c r="IS1" t="s">
-        <v>940</v>
+        <v>920</v>
       </c>
       <c r="IT1" t="s">
-        <v>939</v>
+        <v>919</v>
       </c>
       <c r="IU1" t="s">
-        <v>938</v>
+        <v>918</v>
       </c>
       <c r="IV1" t="s">
-        <v>937</v>
+        <v>917</v>
       </c>
       <c r="IW1" t="s">
-        <v>936</v>
+        <v>916</v>
       </c>
       <c r="IX1" t="s">
-        <v>935</v>
+        <v>915</v>
       </c>
       <c r="IY1" t="s">
-        <v>934</v>
+        <v>914</v>
       </c>
       <c r="IZ1" t="s">
-        <v>933</v>
+        <v>913</v>
       </c>
       <c r="JA1" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="JB1" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
       <c r="JC1" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="JD1" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
       <c r="JE1" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="JF1" t="s">
-        <v>927</v>
+        <v>907</v>
       </c>
       <c r="JG1" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="JH1" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="JI1" t="s">
-        <v>924</v>
+        <v>904</v>
       </c>
       <c r="JJ1" t="s">
-        <v>923</v>
+        <v>903</v>
       </c>
       <c r="JK1" t="s">
-        <v>922</v>
+        <v>902</v>
       </c>
       <c r="JL1" t="s">
-        <v>921</v>
+        <v>901</v>
       </c>
       <c r="JM1" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="JN1" t="s">
-        <v>919</v>
+        <v>899</v>
       </c>
       <c r="JO1" t="s">
-        <v>918</v>
+        <v>898</v>
       </c>
       <c r="JP1" t="s">
-        <v>917</v>
+        <v>897</v>
       </c>
       <c r="JQ1" t="s">
-        <v>916</v>
+        <v>896</v>
       </c>
       <c r="JR1" t="s">
-        <v>915</v>
+        <v>895</v>
       </c>
       <c r="JS1" t="s">
-        <v>914</v>
+        <v>894</v>
       </c>
       <c r="JT1" t="s">
-        <v>913</v>
+        <v>893</v>
       </c>
       <c r="JU1" t="s">
-        <v>912</v>
+        <v>892</v>
       </c>
       <c r="JV1" t="s">
-        <v>911</v>
+        <v>891</v>
       </c>
       <c r="JW1" t="s">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="JX1" t="s">
-        <v>909</v>
+        <v>889</v>
       </c>
       <c r="JY1" t="s">
-        <v>908</v>
+        <v>888</v>
       </c>
       <c r="JZ1" t="s">
-        <v>907</v>
+        <v>887</v>
       </c>
       <c r="KA1" t="s">
-        <v>906</v>
+        <v>886</v>
       </c>
       <c r="KB1" t="s">
-        <v>905</v>
+        <v>885</v>
       </c>
       <c r="KC1" t="s">
-        <v>904</v>
+        <v>884</v>
       </c>
       <c r="KD1" t="s">
-        <v>903</v>
+        <v>883</v>
       </c>
       <c r="KE1" t="s">
-        <v>902</v>
+        <v>882</v>
       </c>
       <c r="KF1" t="s">
-        <v>901</v>
+        <v>881</v>
       </c>
       <c r="KG1" t="s">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="KH1" t="s">
-        <v>899</v>
+        <v>879</v>
       </c>
       <c r="KI1" t="s">
-        <v>898</v>
+        <v>878</v>
       </c>
       <c r="KJ1" t="s">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="KK1" t="s">
-        <v>896</v>
+        <v>876</v>
       </c>
       <c r="KL1" t="s">
-        <v>895</v>
+        <v>875</v>
       </c>
       <c r="KM1" t="s">
-        <v>894</v>
+        <v>874</v>
       </c>
       <c r="KN1" t="s">
-        <v>893</v>
+        <v>873</v>
       </c>
       <c r="KO1" t="s">
-        <v>892</v>
+        <v>872</v>
       </c>
       <c r="KP1" t="s">
-        <v>891</v>
+        <v>871</v>
       </c>
       <c r="KQ1" t="s">
-        <v>890</v>
+        <v>870</v>
       </c>
       <c r="KR1" t="s">
-        <v>889</v>
+        <v>869</v>
       </c>
       <c r="KS1" t="s">
-        <v>888</v>
+        <v>868</v>
       </c>
       <c r="KT1" t="s">
-        <v>887</v>
+        <v>867</v>
       </c>
       <c r="KU1" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="KV1" t="s">
-        <v>885</v>
+        <v>865</v>
       </c>
       <c r="KW1" t="s">
-        <v>884</v>
+        <v>864</v>
       </c>
       <c r="KX1" t="s">
-        <v>883</v>
+        <v>863</v>
       </c>
       <c r="KY1" t="s">
-        <v>882</v>
+        <v>862</v>
       </c>
       <c r="KZ1" t="s">
-        <v>881</v>
+        <v>861</v>
       </c>
       <c r="LA1" t="s">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="LB1" t="s">
-        <v>879</v>
+        <v>859</v>
       </c>
       <c r="LC1" t="s">
-        <v>878</v>
+        <v>858</v>
       </c>
       <c r="LD1" t="s">
-        <v>877</v>
+        <v>857</v>
       </c>
       <c r="LE1" t="s">
-        <v>876</v>
+        <v>856</v>
       </c>
       <c r="LF1" t="s">
-        <v>875</v>
+        <v>855</v>
       </c>
       <c r="LG1" t="s">
-        <v>874</v>
+        <v>854</v>
       </c>
       <c r="LH1" t="s">
-        <v>873</v>
+        <v>853</v>
       </c>
       <c r="LI1" t="s">
-        <v>872</v>
+        <v>852</v>
       </c>
       <c r="LJ1" t="s">
-        <v>871</v>
+        <v>851</v>
       </c>
       <c r="LK1" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="LL1" t="s">
-        <v>869</v>
+        <v>849</v>
       </c>
       <c r="LM1" t="s">
-        <v>868</v>
+        <v>848</v>
       </c>
       <c r="LN1" t="s">
-        <v>867</v>
+        <v>847</v>
       </c>
       <c r="LO1" t="s">
-        <v>866</v>
+        <v>846</v>
       </c>
       <c r="LP1" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="LQ1" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="LR1" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="LS1" t="s">
-        <v>862</v>
+        <v>842</v>
       </c>
       <c r="LT1" t="s">
-        <v>861</v>
+        <v>841</v>
       </c>
       <c r="LU1" t="s">
-        <v>860</v>
+        <v>840</v>
       </c>
       <c r="LV1" t="s">
-        <v>859</v>
+        <v>839</v>
       </c>
       <c r="LW1" t="s">
-        <v>858</v>
+        <v>838</v>
       </c>
       <c r="LX1" t="s">
-        <v>857</v>
+        <v>837</v>
       </c>
       <c r="LY1" t="s">
-        <v>856</v>
+        <v>836</v>
       </c>
       <c r="LZ1" t="s">
-        <v>855</v>
+        <v>835</v>
       </c>
       <c r="MA1" t="s">
-        <v>854</v>
+        <v>834</v>
       </c>
       <c r="MB1" t="s">
-        <v>853</v>
+        <v>833</v>
       </c>
       <c r="MC1" t="s">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="MD1" t="s">
-        <v>851</v>
+        <v>831</v>
       </c>
       <c r="ME1" t="s">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="MF1" t="s">
-        <v>849</v>
+        <v>829</v>
       </c>
       <c r="MG1" t="s">
-        <v>848</v>
+        <v>828</v>
       </c>
       <c r="MH1" t="s">
-        <v>847</v>
+        <v>827</v>
       </c>
       <c r="MI1" t="s">
-        <v>846</v>
+        <v>826</v>
       </c>
       <c r="MJ1" t="s">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="MK1" t="s">
-        <v>844</v>
+        <v>824</v>
       </c>
       <c r="ML1" t="s">
-        <v>843</v>
+        <v>823</v>
       </c>
       <c r="MM1" t="s">
-        <v>842</v>
+        <v>822</v>
       </c>
       <c r="MN1" t="s">
-        <v>841</v>
+        <v>821</v>
       </c>
       <c r="MO1" t="s">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="MP1" t="s">
-        <v>839</v>
+        <v>819</v>
       </c>
       <c r="MQ1" t="s">
-        <v>838</v>
+        <v>818</v>
       </c>
       <c r="MR1" t="s">
-        <v>837</v>
+        <v>817</v>
       </c>
       <c r="MS1" t="s">
-        <v>836</v>
+        <v>816</v>
       </c>
       <c r="MT1" t="s">
-        <v>835</v>
+        <v>815</v>
       </c>
       <c r="MU1" t="s">
-        <v>834</v>
+        <v>814</v>
       </c>
       <c r="MV1" t="s">
-        <v>833</v>
+        <v>813</v>
       </c>
       <c r="MW1" t="s">
-        <v>832</v>
+        <v>812</v>
       </c>
       <c r="MX1" t="s">
-        <v>831</v>
+        <v>811</v>
       </c>
       <c r="MY1" t="s">
-        <v>830</v>
+        <v>810</v>
       </c>
       <c r="MZ1" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="NA1" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="NB1" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="NC1" t="s">
-        <v>826</v>
+        <v>806</v>
       </c>
       <c r="ND1" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="NE1" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="NF1" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="NG1" t="s">
-        <v>822</v>
+        <v>802</v>
       </c>
       <c r="NH1" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="NI1" t="s">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="NJ1" t="s">
-        <v>819</v>
+        <v>799</v>
       </c>
       <c r="NK1" t="s">
-        <v>818</v>
+        <v>798</v>
       </c>
       <c r="NL1" t="s">
-        <v>817</v>
+        <v>797</v>
       </c>
       <c r="NM1" t="s">
-        <v>816</v>
+        <v>796</v>
       </c>
       <c r="NN1" t="s">
-        <v>815</v>
+        <v>795</v>
       </c>
       <c r="NO1" t="s">
-        <v>814</v>
+        <v>794</v>
       </c>
       <c r="NP1" t="s">
-        <v>813</v>
+        <v>793</v>
       </c>
       <c r="NQ1" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="NR1" t="s">
-        <v>811</v>
+        <v>791</v>
       </c>
       <c r="NS1" t="s">
-        <v>810</v>
+        <v>790</v>
       </c>
       <c r="NT1" t="s">
-        <v>809</v>
+        <v>789</v>
       </c>
       <c r="NU1" t="s">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="NV1" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="NW1" t="s">
-        <v>806</v>
+        <v>786</v>
       </c>
       <c r="NX1" t="s">
-        <v>805</v>
+        <v>785</v>
       </c>
       <c r="NY1" t="s">
-        <v>804</v>
+        <v>784</v>
       </c>
       <c r="NZ1" t="s">
-        <v>803</v>
+        <v>783</v>
       </c>
       <c r="OA1" t="s">
-        <v>802</v>
+        <v>782</v>
       </c>
       <c r="OB1" t="s">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="OC1" t="s">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="OD1" t="s">
-        <v>799</v>
+        <v>779</v>
       </c>
       <c r="OE1" t="s">
-        <v>798</v>
+        <v>778</v>
       </c>
       <c r="OF1" t="s">
-        <v>797</v>
+        <v>777</v>
       </c>
       <c r="OG1" t="s">
-        <v>796</v>
+        <v>776</v>
       </c>
       <c r="OH1" t="s">
-        <v>795</v>
+        <v>775</v>
       </c>
       <c r="OI1" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="OJ1" t="s">
-        <v>793</v>
+        <v>773</v>
       </c>
       <c r="OK1" t="s">
-        <v>792</v>
+        <v>772</v>
       </c>
       <c r="OL1" t="s">
-        <v>791</v>
+        <v>771</v>
       </c>
       <c r="OM1" t="s">
-        <v>790</v>
+        <v>770</v>
       </c>
       <c r="ON1" t="s">
-        <v>789</v>
+        <v>769</v>
       </c>
       <c r="OO1" t="s">
-        <v>788</v>
+        <v>768</v>
       </c>
       <c r="OP1" t="s">
-        <v>787</v>
+        <v>767</v>
       </c>
       <c r="OQ1" t="s">
-        <v>786</v>
+        <v>766</v>
       </c>
       <c r="OR1" t="s">
-        <v>785</v>
+        <v>765</v>
       </c>
       <c r="OS1" t="s">
-        <v>784</v>
+        <v>764</v>
       </c>
       <c r="OT1" t="s">
-        <v>783</v>
+        <v>763</v>
       </c>
       <c r="OU1" t="s">
-        <v>782</v>
+        <v>762</v>
       </c>
       <c r="OV1" t="s">
-        <v>781</v>
+        <v>761</v>
       </c>
       <c r="OW1" t="s">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="OX1" t="s">
-        <v>779</v>
+        <v>759</v>
       </c>
       <c r="OY1" t="s">
-        <v>778</v>
+        <v>758</v>
       </c>
       <c r="OZ1" t="s">
-        <v>777</v>
+        <v>757</v>
       </c>
       <c r="PA1" t="s">
-        <v>776</v>
+        <v>756</v>
       </c>
       <c r="PB1" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
       <c r="PC1" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="PD1" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="PE1" t="s">
-        <v>772</v>
+        <v>752</v>
       </c>
       <c r="PF1" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="PG1" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="PH1" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
       <c r="PI1" t="s">
-        <v>768</v>
+        <v>748</v>
       </c>
       <c r="PJ1" t="s">
-        <v>767</v>
+        <v>747</v>
       </c>
       <c r="PK1" t="s">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="PL1" t="s">
-        <v>765</v>
+        <v>745</v>
       </c>
       <c r="PM1" t="s">
-        <v>764</v>
+        <v>744</v>
       </c>
       <c r="PN1" t="s">
-        <v>763</v>
+        <v>743</v>
       </c>
       <c r="PO1" t="s">
-        <v>762</v>
+        <v>742</v>
       </c>
       <c r="PP1" t="s">
-        <v>761</v>
+        <v>741</v>
       </c>
       <c r="PQ1" t="s">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="PR1" t="s">
-        <v>759</v>
+        <v>739</v>
       </c>
       <c r="PS1" t="s">
-        <v>758</v>
+        <v>738</v>
       </c>
       <c r="PT1" t="s">
-        <v>757</v>
+        <v>737</v>
       </c>
       <c r="PU1" t="s">
-        <v>756</v>
+        <v>736</v>
       </c>
       <c r="PV1" t="s">
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="PW1" t="s">
-        <v>754</v>
+        <v>734</v>
       </c>
       <c r="PX1" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
       <c r="PY1" t="s">
-        <v>752</v>
+        <v>732</v>
       </c>
       <c r="PZ1" t="s">
-        <v>751</v>
+        <v>731</v>
       </c>
       <c r="QA1" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="QB1" t="s">
-        <v>749</v>
+        <v>729</v>
       </c>
       <c r="QC1" t="s">
-        <v>748</v>
+        <v>728</v>
       </c>
       <c r="QD1" t="s">
-        <v>747</v>
+        <v>727</v>
       </c>
       <c r="QE1" t="s">
-        <v>746</v>
+        <v>726</v>
       </c>
       <c r="QF1" t="s">
-        <v>745</v>
+        <v>725</v>
       </c>
       <c r="QG1" t="s">
-        <v>744</v>
+        <v>724</v>
       </c>
       <c r="QH1" t="s">
-        <v>743</v>
+        <v>723</v>
       </c>
       <c r="QI1" t="s">
-        <v>742</v>
+        <v>722</v>
       </c>
       <c r="QJ1" t="s">
-        <v>741</v>
+        <v>721</v>
       </c>
       <c r="QK1" t="s">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="QL1" t="s">
-        <v>739</v>
+        <v>719</v>
       </c>
       <c r="QM1" t="s">
-        <v>738</v>
+        <v>718</v>
       </c>
       <c r="QN1" t="s">
-        <v>737</v>
+        <v>717</v>
       </c>
       <c r="QO1" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="QP1" t="s">
-        <v>735</v>
+        <v>715</v>
       </c>
       <c r="QQ1" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="QR1" t="s">
-        <v>733</v>
+        <v>713</v>
       </c>
       <c r="QS1" t="s">
-        <v>732</v>
+        <v>712</v>
       </c>
       <c r="QT1" t="s">
-        <v>731</v>
+        <v>711</v>
       </c>
       <c r="QU1" t="s">
-        <v>730</v>
+        <v>710</v>
       </c>
       <c r="QV1" t="s">
-        <v>729</v>
+        <v>709</v>
       </c>
       <c r="QW1" t="s">
-        <v>728</v>
+        <v>708</v>
       </c>
       <c r="QX1" t="s">
-        <v>727</v>
+        <v>707</v>
       </c>
       <c r="QY1" t="s">
-        <v>726</v>
+        <v>706</v>
       </c>
       <c r="QZ1" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="RA1" t="s">
-        <v>724</v>
+        <v>704</v>
       </c>
       <c r="RB1" t="s">
-        <v>723</v>
+        <v>703</v>
       </c>
       <c r="RC1" t="s">
-        <v>722</v>
+        <v>702</v>
       </c>
       <c r="RD1" t="s">
-        <v>721</v>
+        <v>701</v>
       </c>
       <c r="RE1" t="s">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="RF1" t="s">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="RG1" t="s">
-        <v>718</v>
+        <v>698</v>
       </c>
       <c r="RH1" t="s">
-        <v>717</v>
+        <v>697</v>
       </c>
       <c r="RI1" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
       <c r="RJ1" t="s">
-        <v>715</v>
+        <v>695</v>
       </c>
       <c r="RK1" t="s">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="RL1" t="s">
-        <v>713</v>
+        <v>693</v>
       </c>
       <c r="RM1" t="s">
-        <v>712</v>
+        <v>692</v>
       </c>
       <c r="RN1" t="s">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="RO1" t="s">
-        <v>710</v>
+        <v>690</v>
       </c>
       <c r="RP1" t="s">
-        <v>709</v>
+        <v>689</v>
       </c>
       <c r="RQ1" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="RR1" t="s">
-        <v>707</v>
+        <v>687</v>
       </c>
       <c r="RS1" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="RT1" t="s">
-        <v>705</v>
+        <v>685</v>
       </c>
       <c r="RU1" t="s">
-        <v>704</v>
+        <v>684</v>
       </c>
       <c r="RV1" t="s">
-        <v>703</v>
+        <v>683</v>
       </c>
       <c r="RW1" t="s">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="RX1" t="s">
-        <v>701</v>
+        <v>681</v>
       </c>
       <c r="RY1" t="s">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="RZ1" t="s">
-        <v>699</v>
+        <v>679</v>
       </c>
       <c r="SA1" t="s">
-        <v>698</v>
+        <v>678</v>
       </c>
       <c r="SB1" t="s">
-        <v>697</v>
+        <v>677</v>
       </c>
       <c r="SC1" t="s">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="SD1" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
       <c r="SE1" t="s">
-        <v>694</v>
+        <v>674</v>
       </c>
       <c r="SF1" t="s">
-        <v>693</v>
+        <v>673</v>
       </c>
       <c r="SG1" t="s">
-        <v>692</v>
+        <v>672</v>
       </c>
       <c r="SH1" t="s">
-        <v>691</v>
+        <v>671</v>
       </c>
       <c r="SI1" t="s">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="SJ1" t="s">
-        <v>689</v>
+        <v>669</v>
       </c>
       <c r="SK1" t="s">
-        <v>688</v>
+        <v>668</v>
       </c>
       <c r="SL1" t="s">
-        <v>687</v>
+        <v>667</v>
       </c>
       <c r="SM1" t="s">
-        <v>686</v>
+        <v>666</v>
       </c>
       <c r="SN1" t="s">
-        <v>685</v>
+        <v>665</v>
       </c>
       <c r="SO1" t="s">
-        <v>684</v>
+        <v>664</v>
       </c>
       <c r="SP1" t="s">
-        <v>683</v>
+        <v>663</v>
       </c>
       <c r="SQ1" t="s">
-        <v>682</v>
+        <v>662</v>
       </c>
       <c r="SR1" t="s">
-        <v>681</v>
+        <v>661</v>
       </c>
       <c r="SS1" t="s">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="ST1" t="s">
-        <v>679</v>
+        <v>659</v>
       </c>
       <c r="SU1" t="s">
-        <v>678</v>
+        <v>658</v>
       </c>
       <c r="SV1" t="s">
-        <v>677</v>
+        <v>657</v>
       </c>
       <c r="SW1" t="s">
-        <v>676</v>
+        <v>656</v>
       </c>
       <c r="SX1" t="s">
-        <v>675</v>
+        <v>655</v>
       </c>
       <c r="SY1" t="s">
-        <v>674</v>
+        <v>654</v>
       </c>
       <c r="SZ1" t="s">
-        <v>673</v>
+        <v>653</v>
       </c>
       <c r="TA1" t="s">
-        <v>672</v>
+        <v>652</v>
       </c>
       <c r="TB1" t="s">
-        <v>671</v>
+        <v>651</v>
       </c>
       <c r="TC1" t="s">
-        <v>670</v>
+        <v>650</v>
       </c>
       <c r="TD1" t="s">
-        <v>669</v>
+        <v>649</v>
       </c>
       <c r="TE1" t="s">
-        <v>668</v>
+        <v>648</v>
       </c>
       <c r="TF1" t="s">
-        <v>667</v>
+        <v>647</v>
       </c>
       <c r="TG1" t="s">
-        <v>666</v>
+        <v>646</v>
       </c>
       <c r="TH1" t="s">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="TI1" t="s">
-        <v>664</v>
+        <v>644</v>
       </c>
       <c r="TJ1" t="s">
-        <v>663</v>
+        <v>643</v>
       </c>
       <c r="TK1" t="s">
-        <v>662</v>
+        <v>642</v>
       </c>
       <c r="TL1" t="s">
-        <v>661</v>
+        <v>641</v>
       </c>
       <c r="TM1" t="s">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="TN1" t="s">
-        <v>659</v>
+        <v>639</v>
       </c>
       <c r="TO1" t="s">
-        <v>658</v>
+        <v>638</v>
       </c>
       <c r="TP1" t="s">
-        <v>657</v>
+        <v>637</v>
       </c>
       <c r="TQ1" t="s">
-        <v>656</v>
+        <v>636</v>
       </c>
       <c r="TR1" t="s">
-        <v>655</v>
+        <v>635</v>
       </c>
       <c r="TS1" t="s">
-        <v>654</v>
+        <v>634</v>
       </c>
       <c r="TT1" t="s">
-        <v>653</v>
+        <v>633</v>
       </c>
       <c r="TU1" t="s">
-        <v>652</v>
+        <v>632</v>
       </c>
       <c r="TV1" t="s">
-        <v>651</v>
+        <v>631</v>
       </c>
       <c r="TW1" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="TX1" t="s">
-        <v>649</v>
+        <v>629</v>
       </c>
       <c r="TY1" t="s">
-        <v>648</v>
+        <v>628</v>
       </c>
       <c r="TZ1" t="s">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="UA1" t="s">
-        <v>646</v>
+        <v>626</v>
       </c>
       <c r="UB1" t="s">
-        <v>645</v>
+        <v>625</v>
       </c>
       <c r="UC1" t="s">
-        <v>644</v>
+        <v>624</v>
       </c>
       <c r="UD1" t="s">
-        <v>643</v>
+        <v>623</v>
       </c>
       <c r="UE1" t="s">
-        <v>642</v>
+        <v>622</v>
       </c>
       <c r="UF1" t="s">
-        <v>641</v>
+        <v>621</v>
       </c>
       <c r="UG1" t="s">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="UH1" t="s">
-        <v>639</v>
+        <v>619</v>
       </c>
       <c r="UI1" t="s">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="UJ1" t="s">
-        <v>637</v>
+        <v>617</v>
       </c>
       <c r="UK1" t="s">
-        <v>636</v>
+        <v>616</v>
       </c>
       <c r="UL1" t="s">
-        <v>635</v>
+        <v>615</v>
       </c>
       <c r="UM1" t="s">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="UN1" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
       <c r="UO1" t="s">
-        <v>632</v>
+        <v>612</v>
       </c>
       <c r="UP1" t="s">
-        <v>631</v>
+        <v>611</v>
       </c>
       <c r="UQ1" t="s">
-        <v>630</v>
+        <v>610</v>
       </c>
       <c r="UR1" t="s">
-        <v>629</v>
+        <v>609</v>
       </c>
       <c r="US1" t="s">
-        <v>628</v>
+        <v>608</v>
       </c>
       <c r="UT1" t="s">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="UU1" t="s">
-        <v>626</v>
+        <v>606</v>
       </c>
       <c r="UV1" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
       <c r="UW1" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="UX1" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="UY1" t="s">
-        <v>622</v>
+        <v>602</v>
       </c>
       <c r="UZ1" t="s">
-        <v>621</v>
+        <v>601</v>
       </c>
       <c r="VA1" t="s">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="VB1" t="s">
-        <v>619</v>
+        <v>599</v>
       </c>
       <c r="VC1" t="s">
-        <v>618</v>
+        <v>598</v>
       </c>
       <c r="VD1" t="s">
-        <v>617</v>
+        <v>597</v>
       </c>
       <c r="VE1" t="s">
-        <v>616</v>
+        <v>596</v>
       </c>
       <c r="VF1" t="s">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="VG1" t="s">
-        <v>614</v>
+        <v>594</v>
       </c>
       <c r="VH1" t="s">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="VI1" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="VJ1" t="s">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="VK1" t="s">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="VL1" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="VM1" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="VN1" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="VO1" t="s">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="VP1" t="s">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="VQ1" t="s">
-        <v>604</v>
+        <v>584</v>
       </c>
       <c r="VR1" t="s">
-        <v>603</v>
+        <v>583</v>
       </c>
       <c r="VS1" t="s">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="VT1" t="s">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="VU1" t="s">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="VV1" t="s">
-        <v>599</v>
+        <v>579</v>
       </c>
       <c r="VW1" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
       <c r="VX1" t="s">
-        <v>597</v>
+        <v>577</v>
       </c>
       <c r="VY1" t="s">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="VZ1" t="s">
-        <v>595</v>
+        <v>575</v>
       </c>
       <c r="WA1" t="s">
-        <v>594</v>
+        <v>574</v>
       </c>
       <c r="WB1" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="WC1" t="s">
-        <v>592</v>
+        <v>572</v>
       </c>
       <c r="WD1" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="WE1" t="s">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="WF1" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="WG1" t="s">
-        <v>588</v>
+        <v>568</v>
       </c>
       <c r="WH1" t="s">
-        <v>587</v>
+        <v>567</v>
       </c>
       <c r="WI1" t="s">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="WJ1" t="s">
-        <v>585</v>
+        <v>565</v>
       </c>
       <c r="WK1" t="s">
-        <v>584</v>
+        <v>564</v>
       </c>
       <c r="WL1" t="s">
-        <v>583</v>
+        <v>563</v>
       </c>
       <c r="WM1" t="s">
-        <v>582</v>
+        <v>562</v>
       </c>
       <c r="WN1" t="s">
-        <v>581</v>
+        <v>561</v>
       </c>
       <c r="WO1" t="s">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="WP1" t="s">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="WQ1" t="s">
-        <v>578</v>
+        <v>558</v>
       </c>
       <c r="WR1" t="s">
-        <v>577</v>
+        <v>557</v>
       </c>
       <c r="WS1" t="s">
-        <v>576</v>
+        <v>556</v>
       </c>
       <c r="WT1" t="s">
-        <v>575</v>
+        <v>555</v>
       </c>
       <c r="WU1" t="s">
-        <v>574</v>
+        <v>554</v>
       </c>
       <c r="WV1" t="s">
-        <v>573</v>
+        <v>553</v>
       </c>
       <c r="WW1" t="s">
-        <v>572</v>
+        <v>552</v>
       </c>
       <c r="WX1" t="s">
-        <v>571</v>
+        <v>551</v>
       </c>
       <c r="WY1" t="s">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="WZ1" t="s">
-        <v>569</v>
+        <v>549</v>
       </c>
       <c r="XA1" t="s">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="XB1" t="s">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="XC1" t="s">
-        <v>566</v>
+        <v>546</v>
       </c>
       <c r="XD1" t="s">
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="XE1" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="XF1" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="XG1" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="XH1" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="XI1" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="XJ1" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="XK1" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="XL1" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="XM1" t="s">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="XN1" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="XO1" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="XP1" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="XQ1" t="s">
-        <v>552</v>
+        <v>532</v>
       </c>
       <c r="XR1" t="s">
-        <v>551</v>
+        <v>531</v>
       </c>
       <c r="XS1" t="s">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="XT1" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="XU1" t="s">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="XV1" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="XW1" t="s">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="XX1" t="s">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="XY1" t="s">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="XZ1" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="YA1" t="s">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="YB1" t="s">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="YC1" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="YD1" t="s">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="YE1" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="YF1" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="YG1" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="YH1" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="YI1" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="YJ1" t="s">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="YK1" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="YL1" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="YM1" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="YN1" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="YO1" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="YP1" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="YQ1" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="YR1" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="YS1" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="YT1" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="YU1" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="YV1" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="YW1" t="s">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="YX1" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="YY1" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="YZ1" t="s">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="ZA1" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="ZB1" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="ZC1" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="ZD1" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="ZE1" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="ZF1" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="ZG1" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="ZH1" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="ZI1" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="ZJ1" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="ZK1" t="s">
-        <v>506</v>
+        <v>486</v>
       </c>
       <c r="ZL1" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="ZM1" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
       <c r="ZN1" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="ZO1" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="ZP1" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="ZQ1" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="ZR1" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="ZS1" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="ZT1" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="ZU1" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="ZV1" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="ZW1" t="s">
-        <v>494</v>
+        <v>474</v>
       </c>
       <c r="ZX1" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="ZY1" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="ZZ1" t="s">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="AAA1" t="s">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="AAB1" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="AAC1" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="AAD1" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="AAE1" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="AAF1" t="s">
-        <v>485</v>
+        <v>465</v>
       </c>
       <c r="AAG1" t="s">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="AAH1" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="AAI1" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="AAJ1" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="AAK1" t="s">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AAL1" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="AAM1" t="s">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="AAN1" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="AAO1" t="s">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="AAP1" t="s">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="AAQ1" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="AAR1" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="AAS1" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="AAT1" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="AAU1" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="AAV1" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="AAW1" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="AAX1" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="AAY1" t="s">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="AAZ1" t="s">
-        <v>465</v>
+        <v>445</v>
       </c>
       <c r="ABA1" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="ABB1" t="s">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="ABC1" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="ABD1" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="ABE1" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="ABF1" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="ABG1" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="ABH1" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="ABI1" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="ABJ1" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="ABK1" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="ABL1" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="ABM1" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="ABN1" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="ABO1" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="ABP1" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="ABQ1" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="ABR1" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="ABS1" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="ABT1" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="ABU1" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="ABV1" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="ABW1" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="ABX1" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="ABY1" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="ABZ1" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="ACA1" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="ACB1" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="ACC1" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="ACD1" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="ACE1" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="ACF1" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="ACG1" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="ACH1" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="ACI1" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="ACJ1" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="ACK1" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="ACL1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="ACM1" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="ACN1" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="ACO1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="ACP1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="ACQ1" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="ACR1" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="ACS1" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="ACT1" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="ACU1" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="ACV1" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="ACW1" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="ACX1" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="ACY1" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="ACZ1" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="ADA1" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="ADB1" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="ADC1" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="ADD1" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="ADE1" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="ADF1" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="ADG1" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="ADH1" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="ADI1" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="ADJ1" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="ADK1" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="ADL1" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="ADM1" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="ADN1" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="ADO1" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="ADP1" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="ADQ1" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="ADR1" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="ADS1" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="ADT1" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="ADU1" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="ADV1" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="ADW1" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="ADX1" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="ADY1" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="ADZ1" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="AEA1" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="AEB1" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="AEC1" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="AED1" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="AEE1" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="AEF1" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="AEG1" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AEH1" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="AEI1" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="AEJ1" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="AEK1" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="AEL1" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="AEM1" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="AEN1" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="AEO1" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="AEP1" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="AEQ1" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AER1" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="AES1" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="AET1" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="AEU1" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="AEV1" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="AEW1" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="AEX1" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="AEY1" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="AEZ1" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="AFA1" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AFB1" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="AFC1" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="AFD1" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="AFE1" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="AFF1" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="AFG1" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="AFH1" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="AFI1" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="AFJ1" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="AFK1" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AFL1" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="AFM1" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="AFN1" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="AFO1" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="AFP1" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="AFQ1" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="AFR1" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="AFS1" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="AFT1" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="AFU1" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AFV1" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="AFW1" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="AFX1" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="AFY1" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="AFZ1" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="AGA1" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="AGB1" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="AGC1" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="AGD1" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="AGE1" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AGF1" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="AGG1" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="AGH1" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="AGI1" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="AGJ1" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="AGK1" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="AGL1" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="AGM1" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="AGN1" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="AGO1" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AGP1" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="AGQ1" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="AGR1" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="AGS1" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="AGT1" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="AGU1" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="AGV1" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="AGW1" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="AGX1" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="AGY1" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AGZ1" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="AHA1" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="AHB1" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="AHC1" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AHD1" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="AHE1" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="AHF1" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="AHG1" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="AHH1" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="AHI1" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AHJ1" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="AHK1" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="AHL1" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="AHM1" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="AHN1" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="AHO1" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="AHP1" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="AHQ1" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="AHR1" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="AHS1" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AHT1" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="AHU1" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="AHV1" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="AHW1" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="AHX1" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="AHY1" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="AHZ1" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="AIA1" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="AIB1" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="AIC1" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AID1" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="AIE1" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="AIF1" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="AIG1" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="AIH1" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="AII1" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="AIJ1" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="AIK1" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="AIL1" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="AIM1" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AIN1" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="AIO1" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="AIP1" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="AIQ1" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="AIR1" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="AIS1" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="AIT1" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="AIU1" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="AIV1" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="AIW1" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AIX1" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="AIY1" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="AIZ1" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="AJA1" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="AJB1" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="AJC1" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="AJD1" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="AJE1" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="AJF1" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="AJG1" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AJH1" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="AJI1" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="AJJ1" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="AJK1" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="AJL1" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="AJM1" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="AJN1" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="AJO1" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="AJP1" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="AJQ1" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AJR1" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="AJS1" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="AJT1" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="AJU1" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="AJV1" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="AJW1" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="AJX1" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="AJY1" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="AJZ1" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="AKA1" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AKB1" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="AKC1" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="AKD1" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="AKE1" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="AKF1" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="AKG1" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="AKH1" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="AKI1" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="AKJ1" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="AKK1" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AKL1" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="AKM1" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="AKN1" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="AKO1" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="AKP1" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="AKQ1" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="AKR1" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="AKS1" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="AKT1" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="AKU1" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AKV1" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="AKW1" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="AKX1" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="AKY1" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="AKZ1" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="ALA1" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="ALB1" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="ALC1" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="ALD1" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="ALE1" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="ALF1" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="ALG1" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="ALH1" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="ALI1" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="ALJ1" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="ALK1" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="ALL1" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="ALM1" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="ALN1" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="ALO1" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="ALP1" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="ALQ1" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="ALR1" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="ALS1" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="ALT1" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="ALU1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="ALV1" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="ALW1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="ALX1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="ALY1" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="ALZ1" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="AMA1" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="AMB1" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="AMC1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="AMD1" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="AME1" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="AMF1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="AMG1" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="AMH1" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="AMI1" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AMJ1" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="AMK1" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="AML1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="AMM1" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="AMN1" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="AMO1" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="AMP1" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="AMQ1" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="AMR1" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="AMS1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AMT1" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="AMU1" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="AMV1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="AMW1" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="AMX1" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="AMY1" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="AMZ1" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="ANA1" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="ANB1" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="ANC1" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AND1" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="ANE1" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="ANF1" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="ANG1" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="ANH1" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="ANI1" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="ANJ1" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="ANK1" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="ANL1" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="ANM1" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="ANN1" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="ANO1" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="ANP1" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="ANQ1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="ANR1" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="ANS1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="ANT1" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="ANU1" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="ANV1" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="ANW1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="ANX1" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="ANY1" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="ANZ1" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="AOA1" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="AOB1" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="AOC1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AOD1" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="AOE1" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="AOF1" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="AOG1" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AOH1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="AOI1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="AOJ1" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="AOK1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="AOL1" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="AOM1" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="AON1" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="AOO1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="AOP1" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="AOQ1" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AOR1" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="AOS1" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="AOT1" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="AOU1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="AOV1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="AOW1" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="AOX1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AOY1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AOZ1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="APA1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="APB1" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="APC1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="APD1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="APE1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="APF1" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="APG1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="APH1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="API1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="APJ1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="APK1" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="APL1" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="APM1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="APN1" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="APO1" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="APP1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="APQ1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="APR1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="APS1" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="APT1" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="APU1" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="APV1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="APW1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="APX1" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="APY1" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="APZ1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AQA1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQB1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQC1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQD1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQE1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQF1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQG1" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:1125" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1118" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>3170</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>4</v>
+      </c>
+      <c r="U2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="V2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Z2">
+        <v>3</v>
+      </c>
+      <c r="AA2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>4.5</v>
+      </c>
+      <c r="AE2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AF2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>1.3</v>
+      </c>
+      <c r="AJ2">
+        <v>1.7</v>
+      </c>
+      <c r="AK2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <v>3.7</v>
+      </c>
+      <c r="AO2">
+        <v>1.9</v>
+      </c>
+      <c r="AP2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR2">
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AT2">
+        <v>3.7</v>
+      </c>
+      <c r="AU2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>4</v>
+      </c>
+      <c r="AY2">
+        <v>2</v>
+      </c>
+      <c r="AZ2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="BB2">
+        <v>1</v>
+      </c>
+      <c r="BC2">
+        <v>2.4</v>
+      </c>
+      <c r="BD2">
+        <v>3.2</v>
+      </c>
+      <c r="BE2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="BF2" s="2"/>
+      <c r="BU2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>43</v>
+      </c>
+      <c r="FI2" t="s">
+        <v>44</v>
+      </c>
+      <c r="FJ2" t="s">
+        <v>43</v>
+      </c>
+      <c r="IW2" t="s">
+        <v>42</v>
+      </c>
+      <c r="IX2" t="s">
+        <v>34</v>
+      </c>
+      <c r="MK2" t="s">
+        <v>41</v>
+      </c>
+      <c r="ML2" t="s">
+        <v>34</v>
+      </c>
+      <c r="PY2" t="s">
+        <v>40</v>
+      </c>
+      <c r="PZ2" t="s">
+        <v>39</v>
+      </c>
+      <c r="TM2" t="s">
+        <v>38</v>
+      </c>
+      <c r="TN2" t="s">
         <v>37</v>
       </c>
-      <c r="D2">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" t="s">
-        <v>56</v>
-      </c>
-      <c r="P2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z2">
+      <c r="XA2" t="s">
+        <v>36</v>
+      </c>
+      <c r="XB2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AAO2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AAP2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AOS2">
+        <v>21.16</v>
+      </c>
+      <c r="AOT2">
+        <v>15.18</v>
+      </c>
+      <c r="AOU2">
+        <v>23.805</v>
+      </c>
+      <c r="AOV2">
+        <v>5.0830000000000002</v>
+      </c>
+      <c r="AOW2">
+        <v>16.169</v>
+      </c>
+      <c r="AOX2">
+        <v>18.722000000000001</v>
+      </c>
+      <c r="AOY2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="AOZ2">
+        <v>17.664000000000001</v>
+      </c>
+      <c r="APD2">
+        <v>21.16</v>
+      </c>
+      <c r="APE2">
+        <v>15.18</v>
+      </c>
+      <c r="APF2">
+        <v>23.805</v>
+      </c>
+      <c r="APG2">
+        <v>5.0830000000000002</v>
+      </c>
+      <c r="APH2">
+        <v>16.169</v>
+      </c>
+      <c r="API2">
+        <v>18.722000000000001</v>
+      </c>
+      <c r="APJ2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="APK2">
+        <v>17.664000000000001</v>
+      </c>
+      <c r="APO2" t="s">
         <v>1</v>
       </c>
-      <c r="AA2">
-        <v>4</v>
-      </c>
-      <c r="AB2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AC2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE2">
+      <c r="APP2" t="s">
         <v>1</v>
       </c>
-      <c r="AF2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="AG2">
-        <v>3</v>
-      </c>
-      <c r="AH2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ2">
+      <c r="APQ2" t="s">
         <v>1</v>
       </c>
-      <c r="AK2">
-        <v>4.5</v>
-      </c>
-      <c r="AL2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AM2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO2">
+      <c r="APR2" t="s">
+        <v>33</v>
+      </c>
+      <c r="APS2" t="s">
         <v>1</v>
       </c>
-      <c r="AP2">
-        <v>1.3</v>
-      </c>
-      <c r="AQ2">
-        <v>1.7</v>
-      </c>
-      <c r="AR2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT2">
+      <c r="APT2" t="s">
         <v>1</v>
       </c>
-      <c r="AU2">
-        <v>3.7</v>
-      </c>
-      <c r="AV2">
-        <v>1.9</v>
-      </c>
-      <c r="AW2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AY2">
+      <c r="APU2" t="s">
         <v>1</v>
-      </c>
-      <c r="AZ2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="BA2">
-        <v>3.7</v>
-      </c>
-      <c r="BB2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="BD2">
-        <v>1</v>
-      </c>
-      <c r="BE2">
-        <v>4</v>
-      </c>
-      <c r="BF2">
-        <v>2</v>
-      </c>
-      <c r="BG2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="BI2">
-        <v>1</v>
-      </c>
-      <c r="BJ2">
-        <v>2.4</v>
-      </c>
-      <c r="BK2">
-        <v>3.2</v>
-      </c>
-      <c r="BL2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="BM2" s="2"/>
-      <c r="CB2" t="s">
-        <v>52</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>50</v>
-      </c>
-      <c r="FP2" t="s">
-        <v>51</v>
-      </c>
-      <c r="FQ2" t="s">
-        <v>50</v>
-      </c>
-      <c r="JD2" t="s">
-        <v>49</v>
-      </c>
-      <c r="JE2" t="s">
-        <v>41</v>
-      </c>
-      <c r="MR2" t="s">
-        <v>48</v>
-      </c>
-      <c r="MS2" t="s">
-        <v>41</v>
-      </c>
-      <c r="QF2" t="s">
-        <v>47</v>
-      </c>
-      <c r="QG2" t="s">
-        <v>46</v>
-      </c>
-      <c r="TT2" t="s">
-        <v>45</v>
-      </c>
-      <c r="TU2" t="s">
-        <v>44</v>
-      </c>
-      <c r="XH2" t="s">
-        <v>43</v>
-      </c>
-      <c r="XI2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AAV2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AAW2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AOZ2">
-        <v>21.16</v>
-      </c>
-      <c r="APA2">
-        <v>15.18</v>
-      </c>
-      <c r="APB2">
-        <v>23.805</v>
-      </c>
-      <c r="APC2">
-        <v>5.0830000000000002</v>
-      </c>
-      <c r="APD2">
-        <v>16.169</v>
-      </c>
-      <c r="APE2">
-        <v>18.722000000000001</v>
-      </c>
-      <c r="APF2">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="APG2">
-        <v>17.664000000000001</v>
-      </c>
-      <c r="APK2">
-        <v>21.16</v>
-      </c>
-      <c r="APL2">
-        <v>15.18</v>
-      </c>
-      <c r="APM2">
-        <v>23.805</v>
-      </c>
-      <c r="APN2">
-        <v>5.0830000000000002</v>
-      </c>
-      <c r="APO2">
-        <v>16.169</v>
-      </c>
-      <c r="APP2">
-        <v>18.722000000000001</v>
-      </c>
-      <c r="APQ2">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="APR2">
-        <v>17.664000000000001</v>
       </c>
       <c r="APV2" t="s">
         <v>1</v>
       </c>
-      <c r="APW2" t="s">
-        <v>1</v>
-      </c>
-      <c r="APX2" t="s">
-        <v>1</v>
-      </c>
-      <c r="APY2" t="s">
-        <v>40</v>
-      </c>
       <c r="APZ2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQB2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQC2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQG2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:1125" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1118" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>778</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3">
-        <v>85</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1174</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" t="s">
-        <v>23</v>
-      </c>
-      <c r="T3" t="s">
-        <v>22</v>
-      </c>
-      <c r="U3" t="s">
-        <v>21</v>
-      </c>
-      <c r="V3" t="s">
         <v>20</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="S3">
+        <v>2</v>
+      </c>
+      <c r="T3">
+        <v>5.56</v>
+      </c>
+      <c r="U3">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="V3">
+        <v>2.33</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="X3">
+        <v>2</v>
+      </c>
+      <c r="Y3">
+        <v>5.75</v>
+      </c>
       <c r="Z3">
+        <v>2.95</v>
+      </c>
+      <c r="AA3">
+        <v>2.36</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC3">
+        <v>1</v>
+      </c>
+      <c r="AD3">
+        <v>3.76</v>
+      </c>
+      <c r="AE3">
+        <v>2.9</v>
+      </c>
+      <c r="AF3">
+        <v>2.37</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH3">
         <v>2</v>
       </c>
-      <c r="AA3">
-        <v>5.56</v>
-      </c>
-      <c r="AB3">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="AC3">
-        <v>2.33</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE3">
+      <c r="AI3">
+        <v>4.7</v>
+      </c>
+      <c r="AJ3">
+        <v>3.47</v>
+      </c>
+      <c r="AK3">
+        <v>2.35</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM3">
         <v>2</v>
       </c>
-      <c r="AF3">
-        <v>5.75</v>
-      </c>
-      <c r="AG3">
-        <v>2.95</v>
-      </c>
-      <c r="AH3">
-        <v>2.36</v>
-      </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AN3">
+        <v>4.72</v>
+      </c>
+      <c r="AO3">
+        <v>2.92</v>
+      </c>
+      <c r="AP3">
+        <v>2.35</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AR3">
+        <v>2</v>
+      </c>
+      <c r="AS3">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="AT3">
+        <v>3.51</v>
+      </c>
+      <c r="AU3">
+        <v>2.35</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AW3">
+        <v>1</v>
+      </c>
+      <c r="AX3">
+        <v>1.88</v>
+      </c>
+      <c r="AY3">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ3">
+        <v>2.9</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB3">
+        <v>2</v>
+      </c>
+      <c r="BC3">
+        <v>4.12</v>
+      </c>
+      <c r="BD3">
+        <v>2.48</v>
+      </c>
+      <c r="BE3">
+        <v>2.77</v>
+      </c>
+      <c r="BF3" s="2"/>
+      <c r="BU3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>17</v>
+      </c>
+      <c r="FI3" t="s">
+        <v>16</v>
+      </c>
+      <c r="FJ3" t="s">
+        <v>15</v>
+      </c>
+      <c r="IW3" t="s">
         <v>14</v>
       </c>
-      <c r="AJ3">
+      <c r="IX3" t="s">
+        <v>13</v>
+      </c>
+      <c r="MK3" t="s">
+        <v>12</v>
+      </c>
+      <c r="ML3" t="s">
+        <v>11</v>
+      </c>
+      <c r="PY3" t="s">
+        <v>10</v>
+      </c>
+      <c r="PZ3" t="s">
+        <v>9</v>
+      </c>
+      <c r="TM3" t="s">
+        <v>8</v>
+      </c>
+      <c r="TN3" t="s">
+        <v>7</v>
+      </c>
+      <c r="TP3" t="s">
+        <v>6</v>
+      </c>
+      <c r="TR3" t="s">
+        <v>5</v>
+      </c>
+      <c r="VD3">
+        <v>0</v>
+      </c>
+      <c r="VF3">
+        <v>0</v>
+      </c>
+      <c r="VH3">
+        <v>0</v>
+      </c>
+      <c r="VJ3">
+        <v>0</v>
+      </c>
+      <c r="VL3">
+        <v>0</v>
+      </c>
+      <c r="VN3">
+        <v>0</v>
+      </c>
+      <c r="VP3">
+        <v>0</v>
+      </c>
+      <c r="VR3">
+        <v>0</v>
+      </c>
+      <c r="VT3">
+        <v>0</v>
+      </c>
+      <c r="VV3">
+        <v>0</v>
+      </c>
+      <c r="XA3" t="s">
+        <v>4</v>
+      </c>
+      <c r="XB3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AAO3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AAP3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AOS3">
+        <v>59.073887999999997</v>
+      </c>
+      <c r="AOT3">
+        <v>40.031500000000001</v>
+      </c>
+      <c r="AOU3">
+        <v>25.842479999999998</v>
+      </c>
+      <c r="AOV3">
+        <v>38.326149999999998</v>
+      </c>
+      <c r="AOW3">
+        <v>32.388640000000002</v>
+      </c>
+      <c r="AOX3">
+        <v>40.747590000000002</v>
+      </c>
+      <c r="AOY3">
+        <v>11.06756</v>
+      </c>
+      <c r="AOZ3">
+        <v>28.302752000000002</v>
+      </c>
+      <c r="APD3">
+        <v>29.536943999999998</v>
+      </c>
+      <c r="APE3">
+        <v>20.015750000000001</v>
+      </c>
+      <c r="APF3">
+        <v>25.842479999999998</v>
+      </c>
+      <c r="APG3">
+        <v>19.163074999999999</v>
+      </c>
+      <c r="APH3">
+        <v>16.194320000000001</v>
+      </c>
+      <c r="API3">
+        <v>20.373795000000001</v>
+      </c>
+      <c r="APJ3">
+        <v>11.06756</v>
+      </c>
+      <c r="APK3">
+        <v>14.151376000000001</v>
+      </c>
+      <c r="APO3" t="s">
         <v>1</v>
       </c>
-      <c r="AK3">
-        <v>3.76</v>
-      </c>
-      <c r="AL3">
-        <v>2.9</v>
-      </c>
-      <c r="AM3">
-        <v>2.37</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO3">
-        <v>2</v>
-      </c>
-      <c r="AP3">
-        <v>4.7</v>
-      </c>
-      <c r="AQ3">
-        <v>3.47</v>
-      </c>
-      <c r="AR3">
-        <v>2.35</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="AT3">
-        <v>2</v>
-      </c>
-      <c r="AU3">
-        <v>4.72</v>
-      </c>
-      <c r="AV3">
-        <v>2.92</v>
-      </c>
-      <c r="AW3">
-        <v>2.35</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="AY3">
-        <v>2</v>
-      </c>
-      <c r="AZ3">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="BA3">
-        <v>3.51</v>
-      </c>
-      <c r="BB3">
-        <v>2.35</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="BD3">
+      <c r="APP3" t="s">
         <v>1</v>
       </c>
-      <c r="BE3">
-        <v>1.88</v>
-      </c>
-      <c r="BF3">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="BG3">
-        <v>2.9</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="BI3">
-        <v>2</v>
-      </c>
-      <c r="BJ3">
-        <v>4.12</v>
-      </c>
-      <c r="BK3">
-        <v>2.48</v>
-      </c>
-      <c r="BL3">
-        <v>2.77</v>
-      </c>
-      <c r="BM3" s="2"/>
-      <c r="CB3" t="s">
-        <v>18</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>17</v>
-      </c>
-      <c r="FP3" t="s">
-        <v>16</v>
-      </c>
-      <c r="FQ3" t="s">
-        <v>15</v>
-      </c>
-      <c r="JD3" t="s">
-        <v>14</v>
-      </c>
-      <c r="JE3" t="s">
-        <v>13</v>
-      </c>
-      <c r="MR3" t="s">
-        <v>12</v>
-      </c>
-      <c r="MS3" t="s">
-        <v>11</v>
-      </c>
-      <c r="QF3" t="s">
-        <v>10</v>
-      </c>
-      <c r="QG3" t="s">
-        <v>9</v>
-      </c>
-      <c r="TT3" t="s">
-        <v>8</v>
-      </c>
-      <c r="TU3" t="s">
-        <v>7</v>
-      </c>
-      <c r="TW3" t="s">
-        <v>6</v>
-      </c>
-      <c r="TY3" t="s">
-        <v>5</v>
-      </c>
-      <c r="VK3">
-        <v>0</v>
-      </c>
-      <c r="VM3">
-        <v>0</v>
-      </c>
-      <c r="VO3">
-        <v>0</v>
-      </c>
-      <c r="VQ3">
-        <v>0</v>
-      </c>
-      <c r="VS3">
-        <v>0</v>
-      </c>
-      <c r="VU3">
-        <v>0</v>
-      </c>
-      <c r="VW3">
-        <v>0</v>
-      </c>
-      <c r="VY3">
-        <v>0</v>
-      </c>
-      <c r="WA3">
-        <v>0</v>
-      </c>
-      <c r="WC3">
-        <v>0</v>
-      </c>
-      <c r="XH3" t="s">
-        <v>4</v>
-      </c>
-      <c r="XI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AAV3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AAW3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AOZ3">
-        <v>59.073887999999997</v>
-      </c>
-      <c r="APA3">
-        <v>40.031500000000001</v>
-      </c>
-      <c r="APB3">
-        <v>25.842479999999998</v>
-      </c>
-      <c r="APC3">
-        <v>38.326149999999998</v>
-      </c>
-      <c r="APD3">
-        <v>32.388640000000002</v>
-      </c>
-      <c r="APE3">
-        <v>40.747590000000002</v>
-      </c>
-      <c r="APF3">
-        <v>11.06756</v>
-      </c>
-      <c r="APG3">
-        <v>28.302752000000002</v>
-      </c>
-      <c r="APK3">
-        <v>29.536943999999998</v>
-      </c>
-      <c r="APL3">
-        <v>20.015750000000001</v>
-      </c>
-      <c r="APM3">
-        <v>25.842479999999998</v>
-      </c>
-      <c r="APN3">
-        <v>19.163074999999999</v>
-      </c>
-      <c r="APO3">
-        <v>16.194320000000001</v>
-      </c>
-      <c r="APP3">
-        <v>20.373795000000001</v>
-      </c>
-      <c r="APQ3">
-        <v>11.06756</v>
-      </c>
-      <c r="APR3">
-        <v>14.151376000000001</v>
+      <c r="APQ3" t="s">
+        <v>1</v>
+      </c>
+      <c r="APR3" t="s">
+        <v>1</v>
+      </c>
+      <c r="APS3" t="s">
+        <v>1</v>
+      </c>
+      <c r="APT3" t="s">
+        <v>1</v>
+      </c>
+      <c r="APU3" t="s">
+        <v>1</v>
       </c>
       <c r="APV3" t="s">
         <v>1</v>
       </c>
-      <c r="APW3" t="s">
-        <v>1</v>
-      </c>
-      <c r="APX3" t="s">
-        <v>1</v>
-      </c>
-      <c r="APY3" t="s">
-        <v>1</v>
-      </c>
-      <c r="APZ3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQA3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQB3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQC3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQG3" s="1" t="s">
+      <c r="APZ3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{7E514458-27D4-43B1-B22E-2163A5A3F26C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/etl/3_carga/pruebacarga.xlsx
+++ b/etl/3_carga/pruebacarga.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quantum-Malloco\mediociones-confort-termico\etl\3_carga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FD66F0-376F-4788-80FC-3E8BF597EE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC365D70-1B30-4A68-89D5-CAD05903E116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7886A274-FF15-4EC9-B530-506EFDDC984E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7886A274-FF15-4EC9-B530-506EFDDC984E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -3944,6 +3944,10 @@
     <col min="5" max="5" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1118" x14ac:dyDescent="0.25">

--- a/etl/3_carga/pruebacarga.xlsx
+++ b/etl/3_carga/pruebacarga.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quantum-Malloco\mediociones-confort-termico\etl\3_carga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14AFD28-0F30-47A8-B1DF-3944D137AC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DE4E2A-51EE-4814-9942-677348EF50B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{18E0EBB0-436E-4D78-9D3E-EA142A3ADEC0}"/>
   </bookViews>
@@ -3480,17 +3480,25 @@
     <t>Celosía</t>
   </si>
   <si>
-    <t>Claudio.San.Martin@ist.cl</t>
+    <t>claudio.sanmartin@ist.cl</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3519,14 +3527,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -7219,7 +7230,7 @@
       <c r="D2" t="s">
         <v>1138</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>1146</v>
       </c>
       <c r="F2" t="s">
@@ -7508,6 +7519,9 @@
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{5977BDB2-2722-4E0A-B406-453D0830B6DA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/etl/3_carga/pruebacarga.xlsx
+++ b/etl/3_carga/pruebacarga.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quantum-Malloco\mediociones-confort-termico\etl\3_carga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4140BADE-D184-4C76-B591-2342906A9FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B938CD-B2A4-4144-AB6E-1AC16EA9CD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A0AD6979-B112-4C7B-BDA0-D296A65DDEEE}"/>
   </bookViews>
@@ -3930,1025 +3930,7 @@
     <col min="70" max="70" width="11" bestFit="1" customWidth="1"/>
     <col min="71" max="71" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="72" max="72" width="10" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="25" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="111" max="111" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="112" max="112" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="21" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="21" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="21" bestFit="1" customWidth="1"/>
-    <col min="120" max="120" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="21" bestFit="1" customWidth="1"/>
-    <col min="122" max="122" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="123" max="123" width="21" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="21" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="21" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="129" max="129" width="21" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="21" bestFit="1" customWidth="1"/>
-    <col min="132" max="132" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="21" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="135" max="135" width="21" bestFit="1" customWidth="1"/>
-    <col min="136" max="136" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="21" bestFit="1" customWidth="1"/>
-    <col min="138" max="138" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="21" bestFit="1" customWidth="1"/>
-    <col min="140" max="140" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="21" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="21" bestFit="1" customWidth="1"/>
-    <col min="144" max="144" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="145" max="145" width="21" bestFit="1" customWidth="1"/>
-    <col min="146" max="146" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="147" max="147" width="21" bestFit="1" customWidth="1"/>
-    <col min="148" max="148" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="21" bestFit="1" customWidth="1"/>
-    <col min="150" max="150" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="151" max="151" width="21" bestFit="1" customWidth="1"/>
-    <col min="152" max="152" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="21" bestFit="1" customWidth="1"/>
-    <col min="154" max="154" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="21" bestFit="1" customWidth="1"/>
-    <col min="156" max="156" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="21" bestFit="1" customWidth="1"/>
-    <col min="158" max="158" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="159" max="159" width="21" bestFit="1" customWidth="1"/>
-    <col min="160" max="160" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="21" bestFit="1" customWidth="1"/>
-    <col min="162" max="162" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="163" max="163" width="21" bestFit="1" customWidth="1"/>
-    <col min="164" max="164" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="165" max="165" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="166" max="166" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="167" max="167" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="168" max="168" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="169" max="169" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="170" max="170" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="171" max="171" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="172" max="172" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="173" max="173" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="174" max="174" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="175" max="175" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="176" max="176" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="177" max="177" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="178" max="178" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="179" max="179" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="180" max="180" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="181" max="181" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="182" max="182" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="183" max="183" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="184" max="184" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="185" max="185" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="186" max="186" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="187" max="187" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="188" max="188" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="189" max="189" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="190" max="190" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="191" max="191" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="192" max="192" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="193" max="193" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="194" max="194" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="195" max="195" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="196" max="196" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="197" max="197" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="198" max="198" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="199" max="199" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="200" max="200" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="201" max="201" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="202" max="202" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="203" max="203" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="204" max="204" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="205" max="205" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="206" max="206" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="207" max="207" width="21" bestFit="1" customWidth="1"/>
-    <col min="208" max="208" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="209" max="209" width="21" bestFit="1" customWidth="1"/>
-    <col min="210" max="210" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="211" max="211" width="21" bestFit="1" customWidth="1"/>
-    <col min="212" max="212" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="213" max="213" width="21" bestFit="1" customWidth="1"/>
-    <col min="214" max="214" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="215" max="215" width="21" bestFit="1" customWidth="1"/>
-    <col min="216" max="216" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="217" max="217" width="21" bestFit="1" customWidth="1"/>
-    <col min="218" max="218" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="219" max="219" width="21" bestFit="1" customWidth="1"/>
-    <col min="220" max="220" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="221" max="221" width="21" bestFit="1" customWidth="1"/>
-    <col min="222" max="222" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="223" max="223" width="21" bestFit="1" customWidth="1"/>
-    <col min="224" max="224" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="225" max="225" width="21" bestFit="1" customWidth="1"/>
-    <col min="226" max="226" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="227" max="227" width="21" bestFit="1" customWidth="1"/>
-    <col min="228" max="228" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="229" max="229" width="21" bestFit="1" customWidth="1"/>
-    <col min="230" max="230" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="231" max="231" width="21" bestFit="1" customWidth="1"/>
-    <col min="232" max="232" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="233" max="233" width="21" bestFit="1" customWidth="1"/>
-    <col min="234" max="234" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="235" max="235" width="21" bestFit="1" customWidth="1"/>
-    <col min="236" max="236" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="237" max="237" width="21" bestFit="1" customWidth="1"/>
-    <col min="238" max="238" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="239" max="239" width="21" bestFit="1" customWidth="1"/>
-    <col min="240" max="240" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="241" max="241" width="21" bestFit="1" customWidth="1"/>
-    <col min="242" max="242" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="243" max="243" width="21" bestFit="1" customWidth="1"/>
-    <col min="244" max="244" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="245" max="245" width="21" bestFit="1" customWidth="1"/>
-    <col min="246" max="246" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="247" max="247" width="21" bestFit="1" customWidth="1"/>
-    <col min="248" max="248" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="249" max="249" width="21" bestFit="1" customWidth="1"/>
-    <col min="250" max="250" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="251" max="251" width="21" bestFit="1" customWidth="1"/>
-    <col min="252" max="252" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="253" max="253" width="21" bestFit="1" customWidth="1"/>
-    <col min="254" max="254" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="255" max="255" width="21" bestFit="1" customWidth="1"/>
-    <col min="256" max="256" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="257" max="257" width="29" bestFit="1" customWidth="1"/>
-    <col min="258" max="258" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="259" max="259" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="260" max="260" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="261" max="261" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="262" max="262" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="263" max="263" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="264" max="264" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="265" max="265" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="266" max="266" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="267" max="267" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="268" max="268" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="269" max="269" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="270" max="270" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="271" max="271" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="272" max="272" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="273" max="273" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="274" max="274" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="275" max="275" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="276" max="276" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="277" max="277" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="278" max="278" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="279" max="279" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="280" max="280" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="281" max="281" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="282" max="282" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="283" max="283" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="284" max="284" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="285" max="285" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="286" max="286" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="287" max="287" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="288" max="288" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="289" max="289" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="290" max="290" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="291" max="291" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="292" max="292" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="293" max="293" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="294" max="294" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="295" max="295" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="296" max="296" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="297" max="297" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="298" max="298" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="299" max="299" width="21" bestFit="1" customWidth="1"/>
-    <col min="300" max="300" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="301" max="301" width="21" bestFit="1" customWidth="1"/>
-    <col min="302" max="302" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="303" max="303" width="21" bestFit="1" customWidth="1"/>
-    <col min="304" max="304" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="305" max="305" width="21" bestFit="1" customWidth="1"/>
-    <col min="306" max="306" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="307" max="307" width="21" bestFit="1" customWidth="1"/>
-    <col min="308" max="308" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="309" max="309" width="21" bestFit="1" customWidth="1"/>
-    <col min="310" max="310" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="311" max="311" width="21" bestFit="1" customWidth="1"/>
-    <col min="312" max="312" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="313" max="313" width="21" bestFit="1" customWidth="1"/>
-    <col min="314" max="314" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="315" max="315" width="21" bestFit="1" customWidth="1"/>
-    <col min="316" max="316" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="317" max="317" width="21" bestFit="1" customWidth="1"/>
-    <col min="318" max="318" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="319" max="319" width="21" bestFit="1" customWidth="1"/>
-    <col min="320" max="320" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="321" max="321" width="21" bestFit="1" customWidth="1"/>
-    <col min="322" max="322" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="323" max="323" width="21" bestFit="1" customWidth="1"/>
-    <col min="324" max="324" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="325" max="325" width="21" bestFit="1" customWidth="1"/>
-    <col min="326" max="326" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="327" max="327" width="21" bestFit="1" customWidth="1"/>
-    <col min="328" max="328" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="329" max="329" width="21" bestFit="1" customWidth="1"/>
-    <col min="330" max="330" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="331" max="331" width="21" bestFit="1" customWidth="1"/>
-    <col min="332" max="332" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="333" max="333" width="21" bestFit="1" customWidth="1"/>
-    <col min="334" max="334" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="335" max="335" width="21" bestFit="1" customWidth="1"/>
-    <col min="336" max="336" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="337" max="337" width="21" bestFit="1" customWidth="1"/>
-    <col min="338" max="338" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="339" max="339" width="21" bestFit="1" customWidth="1"/>
-    <col min="340" max="340" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="341" max="341" width="21" bestFit="1" customWidth="1"/>
-    <col min="342" max="342" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="343" max="343" width="21" bestFit="1" customWidth="1"/>
-    <col min="344" max="344" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="345" max="345" width="21" bestFit="1" customWidth="1"/>
-    <col min="346" max="346" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="347" max="347" width="21" bestFit="1" customWidth="1"/>
-    <col min="348" max="348" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="349" max="349" width="34" bestFit="1" customWidth="1"/>
-    <col min="350" max="350" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="351" max="351" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="352" max="352" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="353" max="353" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="354" max="354" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="355" max="355" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="356" max="356" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="357" max="357" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="358" max="358" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="359" max="359" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="360" max="360" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="361" max="361" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="362" max="362" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="363" max="363" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="364" max="364" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="365" max="365" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="366" max="366" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="367" max="367" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="368" max="368" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="369" max="369" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="370" max="370" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="371" max="371" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="372" max="372" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="373" max="373" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="374" max="374" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="375" max="375" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="376" max="376" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="377" max="377" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="378" max="378" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="379" max="379" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="380" max="380" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="381" max="381" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="382" max="382" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="383" max="383" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="384" max="384" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="385" max="385" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="386" max="386" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="387" max="387" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="388" max="388" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="389" max="389" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="390" max="390" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="391" max="391" width="21" bestFit="1" customWidth="1"/>
-    <col min="392" max="392" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="393" max="393" width="21" bestFit="1" customWidth="1"/>
-    <col min="394" max="394" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="395" max="395" width="21" bestFit="1" customWidth="1"/>
-    <col min="396" max="396" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="397" max="397" width="21" bestFit="1" customWidth="1"/>
-    <col min="398" max="398" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="399" max="399" width="21" bestFit="1" customWidth="1"/>
-    <col min="400" max="400" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="401" max="401" width="21" bestFit="1" customWidth="1"/>
-    <col min="402" max="402" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="403" max="403" width="21" bestFit="1" customWidth="1"/>
-    <col min="404" max="404" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="405" max="405" width="21" bestFit="1" customWidth="1"/>
-    <col min="406" max="406" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="407" max="407" width="21" bestFit="1" customWidth="1"/>
-    <col min="408" max="408" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="409" max="409" width="21" bestFit="1" customWidth="1"/>
-    <col min="410" max="410" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="411" max="411" width="21" bestFit="1" customWidth="1"/>
-    <col min="412" max="412" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="413" max="413" width="21" bestFit="1" customWidth="1"/>
-    <col min="414" max="414" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="415" max="415" width="21" bestFit="1" customWidth="1"/>
-    <col min="416" max="416" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="417" max="417" width="21" bestFit="1" customWidth="1"/>
-    <col min="418" max="418" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="419" max="419" width="21" bestFit="1" customWidth="1"/>
-    <col min="420" max="420" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="421" max="421" width="21" bestFit="1" customWidth="1"/>
-    <col min="422" max="422" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="423" max="423" width="21" bestFit="1" customWidth="1"/>
-    <col min="424" max="424" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="425" max="425" width="21" bestFit="1" customWidth="1"/>
-    <col min="426" max="426" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="427" max="427" width="21" bestFit="1" customWidth="1"/>
-    <col min="428" max="428" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="429" max="429" width="21" bestFit="1" customWidth="1"/>
-    <col min="430" max="430" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="431" max="431" width="21" bestFit="1" customWidth="1"/>
-    <col min="432" max="432" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="433" max="433" width="21" bestFit="1" customWidth="1"/>
-    <col min="434" max="434" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="435" max="435" width="21" bestFit="1" customWidth="1"/>
-    <col min="436" max="436" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="437" max="437" width="21" bestFit="1" customWidth="1"/>
-    <col min="438" max="438" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="439" max="439" width="21" bestFit="1" customWidth="1"/>
-    <col min="440" max="440" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="441" max="441" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="442" max="442" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="443" max="443" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="444" max="444" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="445" max="445" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="446" max="446" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="447" max="447" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="448" max="448" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="449" max="449" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="450" max="450" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="451" max="451" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="452" max="452" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="453" max="453" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="454" max="454" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="455" max="455" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="456" max="456" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="457" max="457" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="458" max="458" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="459" max="459" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="460" max="460" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="461" max="461" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="462" max="462" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="463" max="463" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="464" max="464" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="465" max="465" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="466" max="466" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="467" max="467" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="468" max="468" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="469" max="469" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="470" max="470" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="471" max="471" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="472" max="472" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="473" max="473" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="474" max="474" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="475" max="475" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="476" max="476" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="477" max="477" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="478" max="478" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="479" max="479" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="480" max="480" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="481" max="481" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="482" max="482" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="483" max="483" width="21" bestFit="1" customWidth="1"/>
-    <col min="484" max="484" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="485" max="485" width="21" bestFit="1" customWidth="1"/>
-    <col min="486" max="486" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="487" max="487" width="21" bestFit="1" customWidth="1"/>
-    <col min="488" max="488" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="489" max="489" width="21" bestFit="1" customWidth="1"/>
-    <col min="490" max="490" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="491" max="491" width="21" bestFit="1" customWidth="1"/>
-    <col min="492" max="492" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="493" max="493" width="21" bestFit="1" customWidth="1"/>
-    <col min="494" max="494" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="495" max="495" width="21" bestFit="1" customWidth="1"/>
-    <col min="496" max="496" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="497" max="497" width="21" bestFit="1" customWidth="1"/>
-    <col min="498" max="498" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="499" max="499" width="21" bestFit="1" customWidth="1"/>
-    <col min="500" max="500" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="501" max="501" width="21" bestFit="1" customWidth="1"/>
-    <col min="502" max="502" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="503" max="503" width="21" bestFit="1" customWidth="1"/>
-    <col min="504" max="504" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="505" max="505" width="21" bestFit="1" customWidth="1"/>
-    <col min="506" max="506" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="507" max="507" width="21" bestFit="1" customWidth="1"/>
-    <col min="508" max="508" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="509" max="509" width="21" bestFit="1" customWidth="1"/>
-    <col min="510" max="510" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="511" max="511" width="21" bestFit="1" customWidth="1"/>
-    <col min="512" max="512" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="513" max="513" width="21" bestFit="1" customWidth="1"/>
-    <col min="514" max="514" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="515" max="515" width="21" bestFit="1" customWidth="1"/>
-    <col min="516" max="516" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="517" max="517" width="21" bestFit="1" customWidth="1"/>
-    <col min="518" max="518" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="519" max="519" width="21" bestFit="1" customWidth="1"/>
-    <col min="520" max="520" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="521" max="521" width="21" bestFit="1" customWidth="1"/>
-    <col min="522" max="522" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="523" max="523" width="21" bestFit="1" customWidth="1"/>
-    <col min="524" max="524" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="525" max="525" width="21" bestFit="1" customWidth="1"/>
-    <col min="526" max="526" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="527" max="527" width="21" bestFit="1" customWidth="1"/>
-    <col min="528" max="528" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="529" max="529" width="21" bestFit="1" customWidth="1"/>
-    <col min="530" max="530" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="531" max="531" width="21" bestFit="1" customWidth="1"/>
-    <col min="532" max="532" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="533" max="533" width="17" bestFit="1" customWidth="1"/>
-    <col min="534" max="534" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="535" max="535" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="536" max="536" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="537" max="537" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="538" max="538" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="539" max="539" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="540" max="540" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="541" max="541" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="542" max="542" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="543" max="543" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="544" max="544" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="545" max="545" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="546" max="546" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="547" max="547" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="548" max="548" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="549" max="549" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="550" max="550" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="551" max="551" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="552" max="552" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="553" max="553" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="554" max="554" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="555" max="555" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="556" max="556" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="557" max="557" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="558" max="558" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="559" max="559" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="560" max="560" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="561" max="561" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="562" max="562" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="563" max="563" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="564" max="564" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="565" max="565" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="566" max="566" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="567" max="567" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="568" max="568" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="569" max="569" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="570" max="570" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="571" max="571" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="572" max="572" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="573" max="573" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="574" max="574" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="575" max="575" width="21" bestFit="1" customWidth="1"/>
-    <col min="576" max="576" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="577" max="577" width="21" bestFit="1" customWidth="1"/>
-    <col min="578" max="578" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="579" max="579" width="21" bestFit="1" customWidth="1"/>
-    <col min="580" max="580" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="581" max="581" width="21" bestFit="1" customWidth="1"/>
-    <col min="582" max="582" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="583" max="583" width="21" bestFit="1" customWidth="1"/>
-    <col min="584" max="584" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="585" max="585" width="21" bestFit="1" customWidth="1"/>
-    <col min="586" max="586" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="587" max="587" width="21" bestFit="1" customWidth="1"/>
-    <col min="588" max="588" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="589" max="589" width="21" bestFit="1" customWidth="1"/>
-    <col min="590" max="590" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="591" max="591" width="21" bestFit="1" customWidth="1"/>
-    <col min="592" max="592" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="593" max="593" width="21" bestFit="1" customWidth="1"/>
-    <col min="594" max="594" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="595" max="595" width="21" bestFit="1" customWidth="1"/>
-    <col min="596" max="596" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="597" max="597" width="21" bestFit="1" customWidth="1"/>
-    <col min="598" max="598" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="599" max="599" width="21" bestFit="1" customWidth="1"/>
-    <col min="600" max="600" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="601" max="601" width="21" bestFit="1" customWidth="1"/>
-    <col min="602" max="602" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="603" max="603" width="21" bestFit="1" customWidth="1"/>
-    <col min="604" max="604" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="605" max="605" width="21" bestFit="1" customWidth="1"/>
-    <col min="606" max="606" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="607" max="607" width="21" bestFit="1" customWidth="1"/>
-    <col min="608" max="608" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="609" max="609" width="21" bestFit="1" customWidth="1"/>
-    <col min="610" max="610" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="611" max="611" width="21" bestFit="1" customWidth="1"/>
-    <col min="612" max="612" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="613" max="613" width="21" bestFit="1" customWidth="1"/>
-    <col min="614" max="614" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="615" max="615" width="21" bestFit="1" customWidth="1"/>
-    <col min="616" max="616" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="617" max="617" width="21" bestFit="1" customWidth="1"/>
-    <col min="618" max="618" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="619" max="619" width="21" bestFit="1" customWidth="1"/>
-    <col min="620" max="620" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="621" max="621" width="21" bestFit="1" customWidth="1"/>
-    <col min="622" max="622" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="623" max="623" width="21" bestFit="1" customWidth="1"/>
-    <col min="624" max="624" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="625" max="625" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="626" max="626" width="149.28515625" bestFit="1" customWidth="1"/>
-    <col min="627" max="627" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="628" max="628" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="629" max="629" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="630" max="630" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="631" max="631" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="632" max="632" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="633" max="633" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="634" max="634" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="635" max="635" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="636" max="636" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="637" max="637" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="638" max="638" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="639" max="639" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="640" max="640" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="641" max="641" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="642" max="642" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="643" max="643" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="644" max="644" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="645" max="645" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="646" max="646" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="647" max="647" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="648" max="648" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="649" max="649" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="650" max="650" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="651" max="651" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="652" max="652" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="653" max="653" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="654" max="654" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="655" max="655" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="656" max="656" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="657" max="657" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="658" max="658" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="659" max="659" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="660" max="660" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="661" max="661" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="662" max="662" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="663" max="663" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="664" max="664" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="665" max="665" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="666" max="666" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="667" max="667" width="21" bestFit="1" customWidth="1"/>
-    <col min="668" max="668" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="669" max="669" width="21" bestFit="1" customWidth="1"/>
-    <col min="670" max="670" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="671" max="671" width="21" bestFit="1" customWidth="1"/>
-    <col min="672" max="672" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="673" max="673" width="21" bestFit="1" customWidth="1"/>
-    <col min="674" max="674" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="675" max="675" width="21" bestFit="1" customWidth="1"/>
-    <col min="676" max="676" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="677" max="677" width="21" bestFit="1" customWidth="1"/>
-    <col min="678" max="678" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="679" max="679" width="21" bestFit="1" customWidth="1"/>
-    <col min="680" max="680" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="681" max="681" width="21" bestFit="1" customWidth="1"/>
-    <col min="682" max="682" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="683" max="683" width="21" bestFit="1" customWidth="1"/>
-    <col min="684" max="684" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="685" max="685" width="21" bestFit="1" customWidth="1"/>
-    <col min="686" max="686" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="687" max="687" width="21" bestFit="1" customWidth="1"/>
-    <col min="688" max="688" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="689" max="689" width="21" bestFit="1" customWidth="1"/>
-    <col min="690" max="690" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="691" max="691" width="21" bestFit="1" customWidth="1"/>
-    <col min="692" max="692" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="693" max="693" width="21" bestFit="1" customWidth="1"/>
-    <col min="694" max="694" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="695" max="695" width="21" bestFit="1" customWidth="1"/>
-    <col min="696" max="696" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="697" max="697" width="21" bestFit="1" customWidth="1"/>
-    <col min="698" max="698" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="699" max="699" width="21" bestFit="1" customWidth="1"/>
-    <col min="700" max="700" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="701" max="701" width="21" bestFit="1" customWidth="1"/>
-    <col min="702" max="702" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="703" max="703" width="21" bestFit="1" customWidth="1"/>
-    <col min="704" max="704" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="705" max="705" width="21" bestFit="1" customWidth="1"/>
-    <col min="706" max="706" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="707" max="707" width="21" bestFit="1" customWidth="1"/>
-    <col min="708" max="708" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="709" max="709" width="21" bestFit="1" customWidth="1"/>
-    <col min="710" max="710" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="711" max="711" width="21" bestFit="1" customWidth="1"/>
-    <col min="712" max="712" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="713" max="713" width="21" bestFit="1" customWidth="1"/>
-    <col min="714" max="714" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="715" max="715" width="21" bestFit="1" customWidth="1"/>
-    <col min="716" max="716" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="717" max="717" width="13" bestFit="1" customWidth="1"/>
-    <col min="718" max="718" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="719" max="719" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="720" max="720" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="721" max="721" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="722" max="722" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="723" max="723" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="724" max="724" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="725" max="725" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="726" max="726" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="727" max="727" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="728" max="728" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="729" max="729" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="730" max="730" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="731" max="731" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="732" max="732" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="733" max="733" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="734" max="734" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="735" max="735" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="736" max="736" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="737" max="737" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="738" max="738" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="739" max="739" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="740" max="740" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="741" max="741" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="742" max="742" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="743" max="743" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="744" max="744" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="745" max="745" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="746" max="746" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="747" max="747" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="748" max="748" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="749" max="749" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="750" max="750" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="751" max="751" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="752" max="752" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="753" max="753" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="754" max="754" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="755" max="755" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="756" max="756" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="757" max="757" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="758" max="758" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="759" max="759" width="21" bestFit="1" customWidth="1"/>
-    <col min="760" max="760" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="761" max="761" width="21" bestFit="1" customWidth="1"/>
-    <col min="762" max="762" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="763" max="763" width="21" bestFit="1" customWidth="1"/>
-    <col min="764" max="764" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="765" max="765" width="21" bestFit="1" customWidth="1"/>
-    <col min="766" max="766" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="767" max="767" width="21" bestFit="1" customWidth="1"/>
-    <col min="768" max="768" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="769" max="769" width="21" bestFit="1" customWidth="1"/>
-    <col min="770" max="770" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="771" max="771" width="21" bestFit="1" customWidth="1"/>
-    <col min="772" max="772" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="773" max="773" width="21" bestFit="1" customWidth="1"/>
-    <col min="774" max="774" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="775" max="775" width="21" bestFit="1" customWidth="1"/>
-    <col min="776" max="776" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="777" max="777" width="21" bestFit="1" customWidth="1"/>
-    <col min="778" max="778" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="779" max="779" width="21" bestFit="1" customWidth="1"/>
-    <col min="780" max="780" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="781" max="781" width="21" bestFit="1" customWidth="1"/>
-    <col min="782" max="782" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="783" max="783" width="21" bestFit="1" customWidth="1"/>
-    <col min="784" max="784" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="785" max="785" width="21" bestFit="1" customWidth="1"/>
-    <col min="786" max="786" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="787" max="787" width="21" bestFit="1" customWidth="1"/>
-    <col min="788" max="788" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="789" max="789" width="21" bestFit="1" customWidth="1"/>
-    <col min="790" max="790" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="791" max="791" width="21" bestFit="1" customWidth="1"/>
-    <col min="792" max="792" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="793" max="793" width="21" bestFit="1" customWidth="1"/>
-    <col min="794" max="794" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="795" max="795" width="21" bestFit="1" customWidth="1"/>
-    <col min="796" max="796" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="797" max="797" width="21" bestFit="1" customWidth="1"/>
-    <col min="798" max="798" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="799" max="799" width="21" bestFit="1" customWidth="1"/>
-    <col min="800" max="800" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="801" max="801" width="21" bestFit="1" customWidth="1"/>
-    <col min="802" max="802" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="803" max="803" width="21" bestFit="1" customWidth="1"/>
-    <col min="804" max="804" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="805" max="805" width="21" bestFit="1" customWidth="1"/>
-    <col min="806" max="806" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="807" max="807" width="21" bestFit="1" customWidth="1"/>
-    <col min="808" max="808" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="809" max="809" width="13" bestFit="1" customWidth="1"/>
-    <col min="810" max="810" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="811" max="811" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="812" max="812" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="813" max="813" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="814" max="814" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="815" max="815" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="816" max="816" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="817" max="817" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="818" max="818" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="819" max="819" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="820" max="820" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="821" max="821" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="822" max="822" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="823" max="823" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="824" max="824" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="825" max="825" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="826" max="826" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="827" max="827" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="828" max="828" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="829" max="829" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="830" max="830" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="831" max="831" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="832" max="832" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="833" max="833" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="834" max="834" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="835" max="835" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="836" max="836" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="837" max="837" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="838" max="838" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="839" max="839" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="840" max="840" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="841" max="841" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="842" max="842" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="843" max="843" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="844" max="844" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="845" max="845" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="846" max="846" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="847" max="847" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="848" max="848" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="849" max="849" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="850" max="850" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="851" max="851" width="21" bestFit="1" customWidth="1"/>
-    <col min="852" max="852" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="853" max="853" width="21" bestFit="1" customWidth="1"/>
-    <col min="854" max="854" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="855" max="855" width="21" bestFit="1" customWidth="1"/>
-    <col min="856" max="856" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="857" max="857" width="21" bestFit="1" customWidth="1"/>
-    <col min="858" max="858" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="859" max="859" width="21" bestFit="1" customWidth="1"/>
-    <col min="860" max="860" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="861" max="861" width="21" bestFit="1" customWidth="1"/>
-    <col min="862" max="862" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="863" max="863" width="21" bestFit="1" customWidth="1"/>
-    <col min="864" max="864" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="865" max="865" width="21" bestFit="1" customWidth="1"/>
-    <col min="866" max="866" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="867" max="867" width="21" bestFit="1" customWidth="1"/>
-    <col min="868" max="868" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="869" max="869" width="21" bestFit="1" customWidth="1"/>
-    <col min="870" max="870" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="871" max="871" width="21" bestFit="1" customWidth="1"/>
-    <col min="872" max="872" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="873" max="873" width="21" bestFit="1" customWidth="1"/>
-    <col min="874" max="874" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="875" max="875" width="21" bestFit="1" customWidth="1"/>
-    <col min="876" max="876" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="877" max="877" width="21" bestFit="1" customWidth="1"/>
-    <col min="878" max="878" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="879" max="879" width="21" bestFit="1" customWidth="1"/>
-    <col min="880" max="880" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="881" max="881" width="21" bestFit="1" customWidth="1"/>
-    <col min="882" max="882" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="883" max="883" width="21" bestFit="1" customWidth="1"/>
-    <col min="884" max="884" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="885" max="885" width="21" bestFit="1" customWidth="1"/>
-    <col min="886" max="886" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="887" max="887" width="21" bestFit="1" customWidth="1"/>
-    <col min="888" max="888" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="889" max="889" width="21" bestFit="1" customWidth="1"/>
-    <col min="890" max="890" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="891" max="891" width="21" bestFit="1" customWidth="1"/>
-    <col min="892" max="892" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="893" max="893" width="21" bestFit="1" customWidth="1"/>
-    <col min="894" max="894" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="895" max="895" width="21" bestFit="1" customWidth="1"/>
-    <col min="896" max="896" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="897" max="897" width="21" bestFit="1" customWidth="1"/>
-    <col min="898" max="898" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="899" max="899" width="21" bestFit="1" customWidth="1"/>
-    <col min="900" max="900" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="901" max="901" width="14" bestFit="1" customWidth="1"/>
-    <col min="902" max="902" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="903" max="903" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="904" max="904" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="905" max="905" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="906" max="906" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="907" max="907" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="908" max="908" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="909" max="909" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="910" max="910" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="911" max="911" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="912" max="912" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="913" max="913" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="914" max="914" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="915" max="915" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="916" max="916" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="917" max="917" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="918" max="918" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="919" max="919" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="920" max="920" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="921" max="921" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="922" max="922" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="923" max="923" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="924" max="924" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="925" max="925" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="926" max="926" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="927" max="927" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="928" max="928" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="929" max="929" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="930" max="930" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="931" max="931" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="932" max="932" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="933" max="933" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="934" max="934" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="935" max="935" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="936" max="936" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="937" max="937" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="938" max="938" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="939" max="939" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="940" max="940" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="941" max="941" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="942" max="942" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="943" max="943" width="22" bestFit="1" customWidth="1"/>
-    <col min="944" max="944" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="945" max="945" width="22" bestFit="1" customWidth="1"/>
-    <col min="946" max="946" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="947" max="947" width="22" bestFit="1" customWidth="1"/>
-    <col min="948" max="948" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="949" max="949" width="22" bestFit="1" customWidth="1"/>
-    <col min="950" max="950" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="951" max="951" width="22" bestFit="1" customWidth="1"/>
-    <col min="952" max="952" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="953" max="953" width="22" bestFit="1" customWidth="1"/>
-    <col min="954" max="954" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="955" max="955" width="22" bestFit="1" customWidth="1"/>
-    <col min="956" max="956" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="957" max="957" width="22" bestFit="1" customWidth="1"/>
-    <col min="958" max="958" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="959" max="959" width="22" bestFit="1" customWidth="1"/>
-    <col min="960" max="960" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="961" max="961" width="22" bestFit="1" customWidth="1"/>
-    <col min="962" max="962" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="963" max="963" width="22" bestFit="1" customWidth="1"/>
-    <col min="964" max="964" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="965" max="965" width="22" bestFit="1" customWidth="1"/>
-    <col min="966" max="966" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="967" max="967" width="22" bestFit="1" customWidth="1"/>
-    <col min="968" max="968" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="969" max="969" width="22" bestFit="1" customWidth="1"/>
-    <col min="970" max="970" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="971" max="971" width="22" bestFit="1" customWidth="1"/>
-    <col min="972" max="972" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="973" max="973" width="22" bestFit="1" customWidth="1"/>
-    <col min="974" max="974" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="975" max="975" width="22" bestFit="1" customWidth="1"/>
-    <col min="976" max="976" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="977" max="977" width="22" bestFit="1" customWidth="1"/>
-    <col min="978" max="978" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="979" max="979" width="22" bestFit="1" customWidth="1"/>
-    <col min="980" max="980" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="981" max="981" width="22" bestFit="1" customWidth="1"/>
-    <col min="982" max="982" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="983" max="983" width="22" bestFit="1" customWidth="1"/>
-    <col min="984" max="984" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="985" max="985" width="22" bestFit="1" customWidth="1"/>
-    <col min="986" max="986" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="987" max="987" width="22" bestFit="1" customWidth="1"/>
-    <col min="988" max="988" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="989" max="989" width="22" bestFit="1" customWidth="1"/>
-    <col min="990" max="990" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="991" max="991" width="22" bestFit="1" customWidth="1"/>
-    <col min="992" max="992" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="993" max="993" width="14" bestFit="1" customWidth="1"/>
-    <col min="994" max="994" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="995" max="995" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="996" max="996" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="997" max="997" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="998" max="998" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="999" max="999" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="1000" max="1000" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="1001" max="1001" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="1002" max="1002" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="1003" max="1003" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="1004" max="1004" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="1005" max="1005" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="1006" max="1006" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="1007" max="1007" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="1008" max="1008" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="1009" max="1009" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="1010" max="1010" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="1011" max="1011" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="1012" max="1012" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="1013" max="1013" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="1014" max="1014" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="1015" max="1015" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="1016" max="1016" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="1017" max="1017" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="1018" max="1018" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="1019" max="1019" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="1020" max="1020" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="1021" max="1021" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="1022" max="1022" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="1023" max="1023" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="1024" max="1024" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="1025" max="1025" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="1026" max="1026" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="1027" max="1027" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="1028" max="1028" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="1029" max="1029" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="1030" max="1030" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="1031" max="1031" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="1032" max="1032" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="1033" max="1033" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="1034" max="1034" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="1035" max="1035" width="22" bestFit="1" customWidth="1"/>
-    <col min="1036" max="1036" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1037" max="1037" width="22" bestFit="1" customWidth="1"/>
-    <col min="1038" max="1038" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1039" max="1039" width="22" bestFit="1" customWidth="1"/>
-    <col min="1040" max="1040" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1041" max="1041" width="22" bestFit="1" customWidth="1"/>
-    <col min="1042" max="1042" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1043" max="1043" width="22" bestFit="1" customWidth="1"/>
-    <col min="1044" max="1044" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1045" max="1045" width="22" bestFit="1" customWidth="1"/>
-    <col min="1046" max="1046" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1047" max="1047" width="22" bestFit="1" customWidth="1"/>
-    <col min="1048" max="1048" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1049" max="1049" width="22" bestFit="1" customWidth="1"/>
-    <col min="1050" max="1050" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1051" max="1051" width="22" bestFit="1" customWidth="1"/>
-    <col min="1052" max="1052" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1053" max="1053" width="22" bestFit="1" customWidth="1"/>
-    <col min="1054" max="1054" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1055" max="1055" width="22" bestFit="1" customWidth="1"/>
-    <col min="1056" max="1056" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1057" max="1057" width="22" bestFit="1" customWidth="1"/>
-    <col min="1058" max="1058" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1059" max="1059" width="22" bestFit="1" customWidth="1"/>
-    <col min="1060" max="1060" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1061" max="1061" width="22" bestFit="1" customWidth="1"/>
-    <col min="1062" max="1062" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1063" max="1063" width="22" bestFit="1" customWidth="1"/>
-    <col min="1064" max="1064" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1065" max="1065" width="22" bestFit="1" customWidth="1"/>
-    <col min="1066" max="1066" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1067" max="1067" width="22" bestFit="1" customWidth="1"/>
-    <col min="1068" max="1068" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1069" max="1069" width="22" bestFit="1" customWidth="1"/>
-    <col min="1070" max="1070" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1071" max="1071" width="22" bestFit="1" customWidth="1"/>
-    <col min="1072" max="1072" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1073" max="1073" width="22" bestFit="1" customWidth="1"/>
-    <col min="1074" max="1074" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1075" max="1075" width="22" bestFit="1" customWidth="1"/>
-    <col min="1076" max="1076" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1077" max="1077" width="22" bestFit="1" customWidth="1"/>
-    <col min="1078" max="1078" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1079" max="1079" width="22" bestFit="1" customWidth="1"/>
-    <col min="1080" max="1080" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1081" max="1081" width="22" bestFit="1" customWidth="1"/>
-    <col min="1082" max="1082" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1083" max="1083" width="22" bestFit="1" customWidth="1"/>
-    <col min="1084" max="1084" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="1085" max="1093" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="1094" max="1095" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="1096" max="1104" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="1105" max="1106" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="1107" max="1115" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="1116" max="1117" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="1118" max="1118" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="73" max="1118" width="5.7109375" customWidth="1"/>
     <col min="1119" max="1125" width="4.28515625" customWidth="1"/>
     <col min="1126" max="1126" width="13.85546875" customWidth="1"/>
   </cols>
